--- a/CombinedDataset.xlsx
+++ b/CombinedDataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stew\Documents\GitHub\HDS5106\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D4ED87-1BA1-4D9E-922F-A4A7A84C1BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF13F25-2B05-476C-8C35-F82C980D928E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{49767931-91A8-468D-A7BA-3084B4A3CD8D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="424">
   <si>
     <t>Country</t>
   </si>
@@ -836,17 +836,488 @@
     <t>GH0816</t>
   </si>
   <si>
+    <t>PopDensity</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>PopDensityUnder5</t>
+  </si>
+  <si>
+    <t>Burkina Faso</t>
+  </si>
+  <si>
+    <t>BF5701</t>
+  </si>
+  <si>
+    <t>BF5702</t>
+  </si>
+  <si>
+    <t>BF5703</t>
+  </si>
+  <si>
+    <t>BF5704</t>
+  </si>
+  <si>
+    <t>BF5301</t>
+  </si>
+  <si>
+    <t>BF5302</t>
+  </si>
+  <si>
+    <t>BF5303</t>
+  </si>
+  <si>
+    <t>BF1300</t>
+  </si>
+  <si>
+    <t>BF4901</t>
+  </si>
+  <si>
+    <t>BF4902</t>
+  </si>
+  <si>
+    <t>BF4903</t>
+  </si>
+  <si>
+    <t>BF4801</t>
+  </si>
+  <si>
+    <t>BF4802</t>
+  </si>
+  <si>
+    <t>BF4803</t>
+  </si>
+  <si>
+    <t>BF5001</t>
+  </si>
+  <si>
+    <t>BF5002</t>
+  </si>
+  <si>
+    <t>BF5003</t>
+  </si>
+  <si>
+    <t>BF5004</t>
+  </si>
+  <si>
+    <t>BF5101</t>
+  </si>
+  <si>
+    <t>BF5102</t>
+  </si>
+  <si>
+    <t>BF5103</t>
+  </si>
+  <si>
+    <t>BF5503</t>
+  </si>
+  <si>
+    <t>BF5501</t>
+  </si>
+  <si>
+    <t>BF5502</t>
+  </si>
+  <si>
+    <t>BF4701</t>
+  </si>
+  <si>
+    <t>BF4702</t>
+  </si>
+  <si>
+    <t>BF5401</t>
+  </si>
+  <si>
+    <t>BF5402</t>
+  </si>
+  <si>
+    <t>BF5403</t>
+  </si>
+  <si>
+    <t>BF5404</t>
+  </si>
+  <si>
+    <t>CI2001</t>
+  </si>
+  <si>
+    <t>CI0101</t>
+  </si>
+  <si>
+    <t>CI3001</t>
+  </si>
+  <si>
+    <t>CI3002</t>
+  </si>
+  <si>
+    <t>CI2401</t>
+  </si>
+  <si>
+    <t>CI0301</t>
+  </si>
+  <si>
+    <t>CI2002</t>
+  </si>
+  <si>
+    <t>CI2402</t>
+  </si>
+  <si>
+    <t>CI2403</t>
+  </si>
+  <si>
+    <t>CI2501</t>
+  </si>
+  <si>
+    <t>CI0201</t>
+  </si>
+  <si>
+    <t>CI1601</t>
+  </si>
+  <si>
+    <t>CI1101</t>
+  </si>
+  <si>
+    <t>CI2003</t>
+  </si>
+  <si>
+    <t>CI3201</t>
+  </si>
+  <si>
+    <t>CI0901</t>
+  </si>
+  <si>
+    <t>CI2701</t>
+  </si>
+  <si>
+    <t>CI1401</t>
+  </si>
+  <si>
+    <t>CI2502</t>
+  </si>
+  <si>
+    <t>CI1102</t>
+  </si>
+  <si>
+    <t>CI2301</t>
+  </si>
+  <si>
+    <t>CI1103</t>
+  </si>
+  <si>
+    <t>CI0801</t>
+  </si>
+  <si>
+    <t>CI0501</t>
+  </si>
+  <si>
+    <t>CI2601</t>
+  </si>
+  <si>
+    <t>CI1701</t>
+  </si>
+  <si>
+    <t>CI1501</t>
+  </si>
+  <si>
+    <t>CI1801</t>
+  </si>
+  <si>
+    <t>CI3202</t>
+  </si>
+  <si>
+    <t>CI1901</t>
+  </si>
+  <si>
+    <t>CI0701</t>
+  </si>
+  <si>
+    <t>CI0601</t>
+  </si>
+  <si>
+    <t>CI2801</t>
+  </si>
+  <si>
+    <t>CI2702</t>
+  </si>
+  <si>
+    <t>CI2201</t>
+  </si>
+  <si>
+    <t>CI0602</t>
+  </si>
+  <si>
+    <t>CI0802</t>
+  </si>
+  <si>
+    <t>CI1602</t>
+  </si>
+  <si>
+    <t>CI1603</t>
+  </si>
+  <si>
+    <t>CI3101</t>
+  </si>
+  <si>
+    <t>CI1201</t>
+  </si>
+  <si>
+    <t>CI1301</t>
+  </si>
+  <si>
+    <t>CI2101</t>
+  </si>
+  <si>
+    <t>CI3003</t>
+  </si>
+  <si>
+    <t>CI1502</t>
+  </si>
+  <si>
+    <t>CI2602</t>
+  </si>
+  <si>
+    <t>CI0902</t>
+  </si>
+  <si>
+    <t>CI2202</t>
+  </si>
+  <si>
+    <t>CI1802</t>
+  </si>
+  <si>
+    <t>CI1503</t>
+  </si>
+  <si>
+    <t>CI3301</t>
+  </si>
+  <si>
+    <t>CI1001</t>
+  </si>
+  <si>
+    <t>CI1702</t>
+  </si>
+  <si>
+    <t>CI3102</t>
+  </si>
+  <si>
+    <t>CI2802</t>
+  </si>
+  <si>
+    <t>CI0401</t>
+  </si>
+  <si>
+    <t>CI2703</t>
+  </si>
+  <si>
+    <t>CI1604</t>
+  </si>
+  <si>
+    <t>CI1402</t>
+  </si>
+  <si>
+    <t>CI0702</t>
+  </si>
+  <si>
+    <t>CI0502</t>
+  </si>
+  <si>
+    <t>CI2203</t>
+  </si>
+  <si>
+    <t>CI1902</t>
+  </si>
+  <si>
+    <t>CI2503</t>
+  </si>
+  <si>
+    <t>CI2803</t>
+  </si>
+  <si>
+    <t>CI2102</t>
+  </si>
+  <si>
+    <t>CI3203</t>
+  </si>
+  <si>
+    <t>CI0703</t>
+  </si>
+  <si>
+    <t>CI2603</t>
+  </si>
+  <si>
+    <t>CI1002</t>
+  </si>
+  <si>
+    <t>CI0803</t>
+  </si>
+  <si>
+    <t>CI1703</t>
+  </si>
+  <si>
+    <t>CI2103</t>
+  </si>
+  <si>
+    <t>CI3103</t>
+  </si>
+  <si>
+    <t>CI0402</t>
+  </si>
+  <si>
+    <t>CI1302</t>
+  </si>
+  <si>
+    <t>CI1903</t>
+  </si>
+  <si>
+    <t>CI1104</t>
+  </si>
+  <si>
+    <t>CI2104</t>
+  </si>
+  <si>
+    <t>CI2901</t>
+  </si>
+  <si>
+    <t>CI1403</t>
+  </si>
+  <si>
+    <t>CI1202</t>
+  </si>
+  <si>
+    <t>CI3302</t>
+  </si>
+  <si>
+    <t>CI2105</t>
+  </si>
+  <si>
+    <t>CI0302</t>
+  </si>
+  <si>
+    <t>CI2804</t>
+  </si>
+  <si>
+    <t>CI2302</t>
+  </si>
+  <si>
+    <t>CI3204</t>
+  </si>
+  <si>
+    <t>CI2604</t>
+  </si>
+  <si>
+    <t>CI0303</t>
+  </si>
+  <si>
+    <t>CI2902</t>
+  </si>
+  <si>
+    <t>CI0903</t>
+  </si>
+  <si>
+    <t>CI1404</t>
+  </si>
+  <si>
+    <t>CI0804</t>
+  </si>
+  <si>
+    <t>CI0503</t>
+  </si>
+  <si>
+    <t>CI3004</t>
+  </si>
+  <si>
+    <t>CI0304</t>
+  </si>
+  <si>
+    <t>CI0603</t>
+  </si>
+  <si>
+    <t>CI0403</t>
+  </si>
+  <si>
+    <t>CI0904</t>
+  </si>
+  <si>
+    <t>CI0604</t>
+  </si>
+  <si>
+    <t>CI1405</t>
+  </si>
+  <si>
+    <t>CI1803</t>
+  </si>
+  <si>
+    <t>CI2404</t>
+  </si>
+  <si>
+    <t>CI0202</t>
+  </si>
+  <si>
+    <t>CI3205</t>
+  </si>
+  <si>
+    <t>CI1804</t>
+  </si>
+  <si>
+    <t>CI2303</t>
+  </si>
+  <si>
+    <t>Ivory Coast</t>
+  </si>
+  <si>
+    <t>BF4601</t>
+  </si>
+  <si>
+    <t>BF4602</t>
+  </si>
+  <si>
+    <t>BF4603</t>
+  </si>
+  <si>
+    <t>BF4604</t>
+  </si>
+  <si>
+    <t>BF4605</t>
+  </si>
+  <si>
+    <t>BF4606</t>
+  </si>
+  <si>
+    <t>BF5201</t>
+  </si>
+  <si>
+    <t>BF5202</t>
+  </si>
+  <si>
+    <t>BF5203</t>
+  </si>
+  <si>
+    <t>BF5204</t>
+  </si>
+  <si>
+    <t>BF5205</t>
+  </si>
+  <si>
+    <t>BF5601</t>
+  </si>
+  <si>
+    <t>BF5602</t>
+  </si>
+  <si>
+    <t>BF5603</t>
+  </si>
+  <si>
+    <t>BF5604</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -858,6 +1329,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -881,10 +1358,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1220,18 +1698,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE93494-9460-4C4F-AAB4-84EDA70370DB}">
-  <dimension ref="A1:E261"/>
+  <dimension ref="A1:G414"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1242,8 +1723,14 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1259,8 +1746,14 @@
       <c r="E2">
         <v>97.155556000000004</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>43.617356409047503</v>
+      </c>
+      <c r="G2">
+        <v>6.1852835246893898</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1276,8 +1769,14 @@
       <c r="E3">
         <v>117.07143000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>23.191209802009698</v>
+      </c>
+      <c r="G3">
+        <v>3.2897105240044699</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1293,8 +1792,14 @@
       <c r="E4">
         <v>86.84375</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>21.471793927686001</v>
+      </c>
+      <c r="G4">
+        <v>3.0475143326446301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1310,8 +1815,14 @@
       <c r="E5">
         <v>92.368415999999996</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>21.4282516661325</v>
+      </c>
+      <c r="G5">
+        <v>3.04084080876068</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1327,8 +1838,14 @@
       <c r="E6">
         <v>76.933329999999998</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>11.493463032793899</v>
+      </c>
+      <c r="G6">
+        <v>1.6288042863573</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1344,8 +1861,14 @@
       <c r="E7">
         <v>74.923069999999996</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <v>9.9859587730084591</v>
+      </c>
+      <c r="G7">
+        <v>1.4146286888019199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1359,10 +1882,16 @@
         <v>161.190101439301</v>
       </c>
       <c r="E8" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F8">
+        <v>17.2825849033444</v>
+      </c>
+      <c r="G8">
+        <v>2.3076367633223098</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1378,8 +1907,14 @@
       <c r="E9">
         <v>126.13793</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <v>10.3522617008254</v>
+      </c>
+      <c r="G9">
+        <v>1.3849098447755199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1393,10 +1928,16 @@
         <v>267.45021231771898</v>
       </c>
       <c r="E10" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F10">
+        <v>7.9397658550832304</v>
+      </c>
+      <c r="G10">
+        <v>1.0615774784482801</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1412,8 +1953,14 @@
       <c r="E11">
         <v>134.38637</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <v>10.243998165651201</v>
+      </c>
+      <c r="G11">
+        <v>1.3715497329161901</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1427,10 +1974,16 @@
         <v>300.10928837589802</v>
       </c>
       <c r="E12" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F12">
+        <v>29.745774418793001</v>
+      </c>
+      <c r="G12">
+        <v>3.9739334783313098</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1446,8 +1999,14 @@
       <c r="E13">
         <v>77.846146000000005</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <v>10.295249313398401</v>
+      </c>
+      <c r="G13">
+        <v>1.37516294946156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1463,8 +2022,14 @@
       <c r="E14">
         <v>92.529409999999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <v>23.578217914151299</v>
+      </c>
+      <c r="G14">
+        <v>3.1637357565660502</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1480,8 +2045,14 @@
       <c r="E15">
         <v>92.250010000000003</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <v>13.8045023243949</v>
+      </c>
+      <c r="G15">
+        <v>1.8478468229148499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1495,10 +2066,16 @@
         <v>328.08692580693997</v>
       </c>
       <c r="E16" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F16">
+        <v>14.2688409295129</v>
+      </c>
+      <c r="G16">
+        <v>1.91059413467049</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1514,8 +2091,14 @@
       <c r="E17">
         <v>120.38460499999999</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <v>10.674407682157799</v>
+      </c>
+      <c r="G17">
+        <v>1.4273190971309</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1529,10 +2112,16 @@
         <v>178.24180198757099</v>
       </c>
       <c r="E18" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F18">
+        <v>14.980974013430099</v>
+      </c>
+      <c r="G18">
+        <v>2.0045598624319401</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1548,8 +2137,14 @@
       <c r="E19">
         <v>117.24325</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <v>14.7619940389527</v>
+      </c>
+      <c r="G19">
+        <v>1.97499135785441</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1565,8 +2160,14 @@
       <c r="E20">
         <v>88.3</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <v>8.1046336818219</v>
+      </c>
+      <c r="G20">
+        <v>1.0820797686646499</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1582,8 +2183,14 @@
       <c r="E21">
         <v>73.075000000000003</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <v>8.1730987507598805</v>
+      </c>
+      <c r="G21">
+        <v>1.0912417568389099</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1599,8 +2206,14 @@
       <c r="E22">
         <v>106.52631</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <v>14.869663167596499</v>
+      </c>
+      <c r="G22">
+        <v>1.9884858884177601</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1616,8 +2229,14 @@
       <c r="E23">
         <v>87</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <v>82.965281051920201</v>
+      </c>
+      <c r="G23">
+        <v>11.073452273331901</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1631,10 +2250,16 @@
         <v>245.33428030303</v>
       </c>
       <c r="E24" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F24">
+        <v>83.930581000000004</v>
+      </c>
+      <c r="G24">
+        <v>11.202292</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1650,8 +2275,14 @@
       <c r="E25">
         <v>111</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <v>11.3862820969069</v>
+      </c>
+      <c r="G25">
+        <v>1.5203474629812399</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1667,8 +2298,14 @@
       <c r="E26">
         <v>112.5625</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <v>20.080246333383499</v>
+      </c>
+      <c r="G26">
+        <v>2.6905025905737099</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1682,10 +2319,16 @@
         <v>246.669022520364</v>
       </c>
       <c r="E27" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F27">
+        <v>7.8914304596774203</v>
+      </c>
+      <c r="G27">
+        <v>1.05364772116935</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1701,8 +2344,14 @@
       <c r="E28">
         <v>97.809520000000006</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <v>7.8459019697512202</v>
+      </c>
+      <c r="G28">
+        <v>1.04757643582737</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1718,8 +2367,14 @@
       <c r="E29">
         <v>115.76472</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <v>12.2468173678404</v>
+      </c>
+      <c r="G29">
+        <v>1.6345592250146099</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1735,8 +2390,14 @@
       <c r="E30">
         <v>131.89473000000001</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <v>11.385581208749301</v>
+      </c>
+      <c r="G30">
+        <v>1.5217176304229401</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -1752,8 +2413,14 @@
       <c r="E31">
         <v>110.49999</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <v>8.5630153075091595</v>
+      </c>
+      <c r="G31">
+        <v>1.1428528932234401</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -1769,8 +2436,14 @@
       <c r="E32">
         <v>92.529409999999999</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <v>7.5907746151084998</v>
+      </c>
+      <c r="G32">
+        <v>1.01312847030511</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -1786,8 +2459,14 @@
       <c r="E33">
         <v>45.659089999999999</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <v>9.5399593760568102</v>
+      </c>
+      <c r="G33">
+        <v>1.2763670935633</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -1801,10 +2480,16 @@
         <v>276.52448939123502</v>
       </c>
       <c r="E34" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F34">
+        <v>5.05564977962963</v>
+      </c>
+      <c r="G34">
+        <v>0.67459267629629605</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -1818,10 +2503,16 @@
         <v>265.48645465253202</v>
       </c>
       <c r="E35" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F35">
+        <v>83.930581000000004</v>
+      </c>
+      <c r="G35">
+        <v>11.202292</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1837,8 +2528,14 @@
       <c r="E36">
         <v>86.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <v>3.32886725074184</v>
+      </c>
+      <c r="G36">
+        <v>0.444283293938109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -1854,8 +2551,14 @@
       <c r="E37">
         <v>100.99999</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <v>80.927394979754595</v>
+      </c>
+      <c r="G37">
+        <v>10.8014701161043</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -1871,8 +2574,14 @@
       <c r="E38">
         <v>46.23809</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <v>9.2753020061417608</v>
+      </c>
+      <c r="G38">
+        <v>1.2388094203584401</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -1886,10 +2595,16 @@
         <v>181.833522340667</v>
       </c>
       <c r="E39" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F39">
+        <v>7.5390069811320704</v>
+      </c>
+      <c r="G39">
+        <v>1.0078308264856299</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -1905,8 +2620,14 @@
       <c r="E40">
         <v>116.5</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <v>13.163891755858501</v>
+      </c>
+      <c r="G40">
+        <v>1.75804320226321</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -1922,8 +2643,14 @@
       <c r="E41">
         <v>72.095230000000001</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <v>7.4574489648802302</v>
+      </c>
+      <c r="G41">
+        <v>0.99586757501015</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -1939,8 +2666,14 @@
       <c r="E42">
         <v>73.741929999999996</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <v>8.6590369351851795</v>
+      </c>
+      <c r="G42">
+        <v>1.15928687214342</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -1954,10 +2687,16 @@
         <v>258.82326454033802</v>
       </c>
       <c r="E43" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F43">
+        <v>79.629384411038203</v>
+      </c>
+      <c r="G43">
+        <v>10.628206200068099</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -1971,10 +2710,16 @@
         <v>279.61352375400799</v>
       </c>
       <c r="E44" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F44">
+        <v>58.326195963515097</v>
+      </c>
+      <c r="G44">
+        <v>7.7848445123577896</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -1990,8 +2735,14 @@
       <c r="E45">
         <v>53.991306000000002</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <v>14.8366054618895</v>
+      </c>
+      <c r="G45">
+        <v>1.98443201186673</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -2007,8 +2758,14 @@
       <c r="E46">
         <v>51.148147999999999</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <v>11.3494629372011</v>
+      </c>
+      <c r="G46">
+        <v>1.51729141783675</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -2024,8 +2781,14 @@
       <c r="E47">
         <v>81.714293999999995</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <v>4.9694269999999996</v>
+      </c>
+      <c r="G47">
+        <v>0.66307300000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -2041,8 +2804,14 @@
       <c r="E48">
         <v>69.95</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48">
+        <v>12.402924776772201</v>
+      </c>
+      <c r="G48">
+        <v>1.6574256444731701</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -2058,8 +2827,14 @@
       <c r="E49">
         <v>60.692309999999999</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49">
+        <v>18.0733626539967</v>
+      </c>
+      <c r="G49">
+        <v>2.4118277511330901</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -2073,10 +2848,16 @@
         <v>254.83497536945799</v>
       </c>
       <c r="E50" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F50">
+        <v>73.702620858914401</v>
+      </c>
+      <c r="G50">
+        <v>9.8371822201684598</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -2092,8 +2873,14 @@
       <c r="E51">
         <v>39.671050000000001</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F51">
+        <v>13.427875143602099</v>
+      </c>
+      <c r="G51">
+        <v>1.90494865583634</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -2107,10 +2894,16 @@
         <v>288.51218169809903</v>
       </c>
       <c r="E52" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F52">
+        <v>15.134568664313599</v>
+      </c>
+      <c r="G52">
+        <v>2.1410593852262698</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -2126,8 +2919,14 @@
       <c r="E53">
         <v>77.12903</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53">
+        <v>15.1401878142377</v>
+      </c>
+      <c r="G53">
+        <v>2.1418518365414001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -2143,8 +2942,14 @@
       <c r="E54">
         <v>98.684209999999993</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <v>17.008143040246999</v>
+      </c>
+      <c r="G54">
+        <v>2.4076526171964301</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -2160,8 +2965,14 @@
       <c r="E55">
         <v>104.333336</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55">
+        <v>19.163061966867499</v>
+      </c>
+      <c r="G55">
+        <v>2.71524607064622</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -2177,8 +2988,14 @@
       <c r="E56">
         <v>116.916664</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56">
+        <v>19.188336</v>
+      </c>
+      <c r="G56">
+        <v>2.7188119999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -2194,8 +3011,14 @@
       <c r="E57">
         <v>47.466667000000001</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57">
+        <v>11.8941547001687</v>
+      </c>
+      <c r="G57">
+        <v>1.6843422233068199</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -2211,8 +3034,14 @@
       <c r="E58">
         <v>56.304347999999997</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58">
+        <v>12.277759</v>
+      </c>
+      <c r="G58">
+        <v>1.737616</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -2228,8 +3057,14 @@
       <c r="E59">
         <v>67.625</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F59">
+        <v>7.53503731029297</v>
+      </c>
+      <c r="G59">
+        <v>1.06809740401853</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -2245,8 +3080,14 @@
       <c r="E60">
         <v>77.303030000000007</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60">
+        <v>9.0661116694107395</v>
+      </c>
+      <c r="G60">
+        <v>1.2845902429809399</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -2262,8 +3103,14 @@
       <c r="E61">
         <v>59.311473999999997</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61">
+        <v>13.414514707176499</v>
+      </c>
+      <c r="G61">
+        <v>1.90147808086785</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -2279,8 +3126,14 @@
       <c r="E62">
         <v>78.31429</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <v>10.401446563333</v>
+      </c>
+      <c r="G62">
+        <v>1.47389548791852</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -2296,8 +3149,14 @@
       <c r="E63">
         <v>45.250003999999997</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63">
+        <v>14.5717976737978</v>
+      </c>
+      <c r="G63">
+        <v>2.06664225513906</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -2313,8 +3172,14 @@
       <c r="E64">
         <v>29.754964999999999</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F64">
+        <v>10.367169068251499</v>
+      </c>
+      <c r="G64">
+        <v>1.47005101550748</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -2330,8 +3195,14 @@
       <c r="E65">
         <v>60.24</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F65">
+        <v>9.1314230988166898</v>
+      </c>
+      <c r="G65">
+        <v>1.29597428129541</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -2347,8 +3218,14 @@
       <c r="E66">
         <v>51.630436000000003</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66">
+        <v>14.9801204409391</v>
+      </c>
+      <c r="G66">
+        <v>2.1242945405355802</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -2364,8 +3241,14 @@
       <c r="E67">
         <v>60.709674999999997</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F67">
+        <v>13.5044332261257</v>
+      </c>
+      <c r="G67">
+        <v>1.91370766956711</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>4</v>
       </c>
@@ -2379,10 +3262,16 @@
         <v>105.728000696764</v>
       </c>
       <c r="E68" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F68">
+        <v>25.251461748837201</v>
+      </c>
+      <c r="G68">
+        <v>3.6332005813953501</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -2398,8 +3287,14 @@
       <c r="E69">
         <v>33.804127000000001</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69">
+        <v>25.2750066425283</v>
+      </c>
+      <c r="G69">
+        <v>3.58515128589368</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>4</v>
       </c>
@@ -2415,8 +3310,14 @@
       <c r="E70">
         <v>46.454548000000003</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F70">
+        <v>11.253612405901199</v>
+      </c>
+      <c r="G70">
+        <v>1.5975520300192401</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -2432,8 +3333,14 @@
       <c r="E71">
         <v>47.29</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F71">
+        <v>13.7047587222836</v>
+      </c>
+      <c r="G71">
+        <v>1.94569044640884</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -2449,8 +3356,14 @@
       <c r="E72">
         <v>92.681820000000002</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F72">
+        <v>7.3300861266582196</v>
+      </c>
+      <c r="G72">
+        <v>1.03670774634559</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>4</v>
       </c>
@@ -2466,8 +3379,14 @@
       <c r="E73">
         <v>89.666659999999993</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F73">
+        <v>7.3011900819289002</v>
+      </c>
+      <c r="G73">
+        <v>1.0342810263255</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>4</v>
       </c>
@@ -2483,8 +3402,14 @@
       <c r="E74">
         <v>111.53846</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F74">
+        <v>12.2962456868822</v>
+      </c>
+      <c r="G74">
+        <v>1.74910621399947</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>4</v>
       </c>
@@ -2500,8 +3425,14 @@
       <c r="E75">
         <v>126.77779</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F75">
+        <v>12.0852887176623</v>
+      </c>
+      <c r="G75">
+        <v>1.7202070081138301</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>4</v>
       </c>
@@ -2517,8 +3448,14 @@
       <c r="E76">
         <v>143.58332999999999</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F76">
+        <v>13.560859930661</v>
+      </c>
+      <c r="G76">
+        <v>1.9279587370179201</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>4</v>
       </c>
@@ -2534,8 +3471,14 @@
       <c r="E77">
         <v>131.83332999999999</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F77">
+        <v>24.4693032587349</v>
+      </c>
+      <c r="G77">
+        <v>3.4789326103390099</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>4</v>
       </c>
@@ -2551,8 +3494,14 @@
       <c r="E78">
         <v>167.12</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F78">
+        <v>21.4795234900803</v>
+      </c>
+      <c r="G78">
+        <v>3.0592053917035602</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>4</v>
       </c>
@@ -2566,10 +3515,16 @@
         <v>156.571476479376</v>
       </c>
       <c r="E79" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F79">
+        <v>15.435546642296099</v>
+      </c>
+      <c r="G79">
+        <v>2.2031673993957699</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>4</v>
       </c>
@@ -2585,8 +3540,14 @@
       <c r="E80">
         <v>151.37143</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F80">
+        <v>15.4917599323355</v>
+      </c>
+      <c r="G80">
+        <v>2.2084342842220099</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -2602,8 +3563,14 @@
       <c r="E81">
         <v>164.40539999999999</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F81">
+        <v>23.750175641634002</v>
+      </c>
+      <c r="G81">
+        <v>3.3861046475205101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -2619,8 +3586,14 @@
       <c r="E82">
         <v>100.888885</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F82">
+        <v>5.2832238308775903</v>
+      </c>
+      <c r="G82">
+        <v>0.74686822312176204</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -2636,8 +3609,14 @@
       <c r="E83">
         <v>65.75</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F83">
+        <v>5.4114262498812096</v>
+      </c>
+      <c r="G83">
+        <v>0.76633812422784497</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -2653,8 +3632,14 @@
       <c r="E84">
         <v>82</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F84">
+        <v>10.2742447721454</v>
+      </c>
+      <c r="G84">
+        <v>1.4644733502870499</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>4</v>
       </c>
@@ -2670,8 +3655,14 @@
       <c r="E85">
         <v>53.666663999999997</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F85">
+        <v>9.2383000434611997</v>
+      </c>
+      <c r="G85">
+        <v>1.3151936860590601</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>4</v>
       </c>
@@ -2687,8 +3678,14 @@
       <c r="E86">
         <v>95.333330000000004</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F86">
+        <v>8.18706837003222</v>
+      </c>
+      <c r="G86">
+        <v>1.16202393609023</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>4</v>
       </c>
@@ -2702,10 +3699,16 @@
         <v>27.0966746176512</v>
       </c>
       <c r="E87" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F87">
+        <v>9.0618436960000004</v>
+      </c>
+      <c r="G87">
+        <v>1.28508928533333</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>4</v>
       </c>
@@ -2721,8 +3724,14 @@
       <c r="E88">
         <v>74.05556</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F88">
+        <v>6.8092791461657001</v>
+      </c>
+      <c r="G88">
+        <v>0.966976635146226</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -2738,8 +3747,14 @@
       <c r="E89">
         <v>114.53333000000001</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F89">
+        <v>9.1631497927475607</v>
+      </c>
+      <c r="G89">
+        <v>1.2995404387726599</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>4</v>
       </c>
@@ -2755,8 +3770,14 @@
       <c r="E90">
         <v>105.14286</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F90">
+        <v>8.7455482035429704</v>
+      </c>
+      <c r="G90">
+        <v>1.2456205217501599</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -2772,8 +3793,14 @@
       <c r="E91">
         <v>79.555549999999997</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F91">
+        <v>8.1449170264525002</v>
+      </c>
+      <c r="G91">
+        <v>1.1561500332682</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>4</v>
       </c>
@@ -2789,8 +3816,14 @@
       <c r="E92">
         <v>156.45160000000001</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F92">
+        <v>7.03620573663025</v>
+      </c>
+      <c r="G92">
+        <v>1.00337320030669</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>4</v>
       </c>
@@ -2806,8 +3839,14 @@
       <c r="E93">
         <v>157.36841999999999</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F93">
+        <v>7.1336785464362897</v>
+      </c>
+      <c r="G93">
+        <v>1.0174810621721699</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>4</v>
       </c>
@@ -2823,8 +3862,14 @@
       <c r="E94">
         <v>131.3125</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F94">
+        <v>30.859985607692298</v>
+      </c>
+      <c r="G94">
+        <v>4.3961296569230797</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -2840,8 +3885,14 @@
       <c r="E95">
         <v>130.18181999999999</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F95">
+        <v>15.2874476429474</v>
+      </c>
+      <c r="G95">
+        <v>2.18266519578947</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -2855,10 +3906,16 @@
         <v>231.56390374331599</v>
       </c>
       <c r="E96" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F96">
+        <v>21.644081179313702</v>
+      </c>
+      <c r="G96">
+        <v>2.9499221295311702</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -2874,8 +3931,14 @@
       <c r="E97">
         <v>106.63158</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F97">
+        <v>21.701594677622001</v>
+      </c>
+      <c r="G97">
+        <v>2.9577310675044299</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>4</v>
       </c>
@@ -2891,8 +3954,14 @@
       <c r="E98">
         <v>172.31818000000001</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F98">
+        <v>36.422851010118798</v>
+      </c>
+      <c r="G98">
+        <v>4.9629680677518699</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>4</v>
       </c>
@@ -2906,10 +3975,16 @@
         <v>251.560149750416</v>
       </c>
       <c r="E99" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F99">
+        <v>15.703055537437599</v>
+      </c>
+      <c r="G99">
+        <v>2.1372227745424301</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>4</v>
       </c>
@@ -2925,8 +4000,14 @@
       <c r="E100">
         <v>88.888890000000004</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F100">
+        <v>4.9772485169403504</v>
+      </c>
+      <c r="G100">
+        <v>0.67831577904801499</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>4</v>
       </c>
@@ -2942,8 +4023,14 @@
       <c r="E101">
         <v>162.95240000000001</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F101">
+        <v>58.6863268749387</v>
+      </c>
+      <c r="G101">
+        <v>8.0021678410985793</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>4</v>
       </c>
@@ -2959,8 +4046,14 @@
       <c r="E102">
         <v>161.61109999999999</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F102">
+        <v>24.5260650947484</v>
+      </c>
+      <c r="G102">
+        <v>3.3405769974293098</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -2976,8 +4069,14 @@
       <c r="E103">
         <v>77.400000000000006</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F103">
+        <v>4.2533865368656096</v>
+      </c>
+      <c r="G103">
+        <v>0.57951125108958002</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>4</v>
       </c>
@@ -2991,10 +4090,16 @@
         <v>237.238538692437</v>
       </c>
       <c r="E104" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F104">
+        <v>20.2744513015179</v>
+      </c>
+      <c r="G104">
+        <v>2.7647917265243098</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>4</v>
       </c>
@@ -3010,8 +4115,14 @@
       <c r="E105">
         <v>107.666664</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F105">
+        <v>20.7543584978322</v>
+      </c>
+      <c r="G105">
+        <v>2.8301330226982899</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>4</v>
       </c>
@@ -3027,8 +4138,14 @@
       <c r="E106">
         <v>113.46666999999999</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F106">
+        <v>15.7450857276718</v>
+      </c>
+      <c r="G106">
+        <v>2.1467399306094901</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>4</v>
       </c>
@@ -3042,10 +4159,16 @@
         <v>130.27641238429601</v>
       </c>
       <c r="E107" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F107">
+        <v>24.605098215686301</v>
+      </c>
+      <c r="G107">
+        <v>3.3510719831932798</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>4</v>
       </c>
@@ -3061,8 +4184,14 @@
       <c r="E108">
         <v>118.68422</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F108">
+        <v>20.224398255474501</v>
+      </c>
+      <c r="G108">
+        <v>2.75923458359402</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -3076,10 +4205,16 @@
         <v>140.84479419546699</v>
       </c>
       <c r="E109" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F109">
+        <v>34.116227648733201</v>
+      </c>
+      <c r="G109">
+        <v>4.6481411076008801</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -3095,8 +4230,14 @@
       <c r="E110">
         <v>153.58332999999999</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F110">
+        <v>25.8721203537477</v>
+      </c>
+      <c r="G110">
+        <v>3.5272646471663598</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>4</v>
       </c>
@@ -3112,8 +4253,14 @@
       <c r="E111">
         <v>73.333336000000003</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F111">
+        <v>18.4804113568979</v>
+      </c>
+      <c r="G111">
+        <v>2.5208044695331</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>4</v>
       </c>
@@ -3127,10 +4274,16 @@
         <v>346.36007124352301</v>
       </c>
       <c r="E112" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F112">
+        <v>18.548859601544098</v>
+      </c>
+      <c r="G112">
+        <v>2.53015578415576</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>4</v>
       </c>
@@ -3146,8 +4299,14 @@
       <c r="E113">
         <v>130.75</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F113">
+        <v>25.738081350074999</v>
+      </c>
+      <c r="G113">
+        <v>3.5090370502248902</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>4</v>
       </c>
@@ -3163,8 +4322,14 @@
       <c r="E114">
         <v>56.95</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F114">
+        <v>18.153769849313498</v>
+      </c>
+      <c r="G114">
+        <v>2.4837856018306601</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>4</v>
       </c>
@@ -3180,8 +4345,14 @@
       <c r="E115">
         <v>50.793100000000003</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F115">
+        <v>36.442914222512499</v>
+      </c>
+      <c r="G115">
+        <v>4.9847224405129396</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>4</v>
       </c>
@@ -3197,8 +4368,14 @@
       <c r="E116">
         <v>71.047614999999993</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F116">
+        <v>7.8758263968045803</v>
+      </c>
+      <c r="G116">
+        <v>1.07274084654823</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>4</v>
       </c>
@@ -3214,8 +4391,14 @@
       <c r="E117">
         <v>71.083336000000003</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F117">
+        <v>8.3390383277812692</v>
+      </c>
+      <c r="G117">
+        <v>1.1355575578252699</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>4</v>
       </c>
@@ -3231,8 +4414,14 @@
       <c r="E118">
         <v>99.083340000000007</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F118">
+        <v>8.9530732414455301</v>
+      </c>
+      <c r="G118">
+        <v>1.21955722433659</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>4</v>
       </c>
@@ -3248,8 +4437,14 @@
       <c r="E119">
         <v>80.272729999999996</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F119">
+        <v>3.79140251589553</v>
+      </c>
+      <c r="G119">
+        <v>0.51578898478920099</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>4</v>
       </c>
@@ -3265,8 +4460,14 @@
       <c r="E120">
         <v>82</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F120">
+        <v>8.3253586352481896</v>
+      </c>
+      <c r="G120">
+        <v>1.1342737746793099</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>4</v>
       </c>
@@ -3280,10 +4481,16 @@
         <v>208.93520112693699</v>
       </c>
       <c r="E121" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F121">
+        <v>8.2189461061522593</v>
+      </c>
+      <c r="G121">
+        <v>1.1197655034242699</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>4</v>
       </c>
@@ -3299,8 +4506,14 @@
       <c r="E122">
         <v>94.200005000000004</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F122">
+        <v>4.0601522940926698</v>
+      </c>
+      <c r="G122">
+        <v>0.55362046630144002</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -3316,8 +4529,14 @@
       <c r="E123">
         <v>76.736850000000004</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F123">
+        <v>13.4413398236372</v>
+      </c>
+      <c r="G123">
+        <v>1.8297769450297801</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -3333,8 +4552,14 @@
       <c r="E124">
         <v>100.78573</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F124">
+        <v>15.5733430474271</v>
+      </c>
+      <c r="G124">
+        <v>2.1232814299264899</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>4</v>
       </c>
@@ -3350,8 +4575,14 @@
       <c r="E125">
         <v>75.636359999999996</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F125">
+        <v>30.5385756896552</v>
+      </c>
+      <c r="G125">
+        <v>4.1685429821200497</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>4</v>
       </c>
@@ -3367,8 +4598,14 @@
       <c r="E126">
         <v>133.66667000000001</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F126">
+        <v>20.5907925349638</v>
+      </c>
+      <c r="G126">
+        <v>2.7929076927316601</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>4</v>
       </c>
@@ -3384,8 +4621,14 @@
       <c r="E127">
         <v>150.5</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F127">
+        <v>22.919171453684001</v>
+      </c>
+      <c r="G127">
+        <v>3.1235656132276199</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>4</v>
       </c>
@@ -3401,8 +4644,14 @@
       <c r="E128">
         <v>81.200005000000004</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F128">
+        <v>7.6577360191487402</v>
+      </c>
+      <c r="G128">
+        <v>1.0431189176876301</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>4</v>
       </c>
@@ -3416,10 +4665,16 @@
         <v>22.936594202898601</v>
       </c>
       <c r="E129" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F129">
+        <v>28.718343999999998</v>
+      </c>
+      <c r="G129">
+        <v>3.3638710000000001</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>4</v>
       </c>
@@ -3433,10 +4688,16 @@
         <v>30.324877486307301</v>
       </c>
       <c r="E130" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F130">
+        <v>27.5751638627784</v>
+      </c>
+      <c r="G130">
+        <v>3.2299931413547598</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -3450,10 +4711,16 @@
         <v>16.169798657718101</v>
       </c>
       <c r="E131" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F131">
+        <v>28.718343999999998</v>
+      </c>
+      <c r="G131">
+        <v>3.3638710000000001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -3467,10 +4734,16 @@
         <v>15.734234234234201</v>
       </c>
       <c r="E132" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F132">
+        <v>28.718343999999998</v>
+      </c>
+      <c r="G132">
+        <v>3.3638710000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>4</v>
       </c>
@@ -3486,8 +4759,14 @@
       <c r="E133">
         <v>32.571426000000002</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F133">
+        <v>4.5171098698219598</v>
+      </c>
+      <c r="G133">
+        <v>0.53020926815617797</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>4</v>
       </c>
@@ -3503,8 +4782,14 @@
       <c r="E134">
         <v>38.375</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F134">
+        <v>4.2931033589479997</v>
+      </c>
+      <c r="G134">
+        <v>0.50527782575574398</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>4</v>
       </c>
@@ -3520,8 +4805,14 @@
       <c r="E135">
         <v>57.5</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F135">
+        <v>3.7213482206499702</v>
+      </c>
+      <c r="G135">
+        <v>0.436785050810654</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>4</v>
       </c>
@@ -3535,10 +4826,16 @@
         <v>31.465319246669701</v>
       </c>
       <c r="E136" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F136">
+        <v>15.837783115475901</v>
+      </c>
+      <c r="G136">
+        <v>1.85691091215195</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>4</v>
       </c>
@@ -3552,10 +4849,16 @@
         <v>30.0285714285714</v>
       </c>
       <c r="E137" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F137">
+        <v>28.718343999999998</v>
+      </c>
+      <c r="G137">
+        <v>3.3638710000000001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -3569,10 +4872,16 @@
         <v>44.426229508196698</v>
       </c>
       <c r="E138" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F138">
+        <v>28.718343999999998</v>
+      </c>
+      <c r="G138">
+        <v>3.3638710000000001</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>4</v>
       </c>
@@ -3586,10 +4895,16 @@
         <v>25.499133448873501</v>
       </c>
       <c r="E139" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F139">
+        <v>28.718343999999998</v>
+      </c>
+      <c r="G139">
+        <v>3.3638710000000001</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>4</v>
       </c>
@@ -3605,8 +4920,14 @@
       <c r="E140">
         <v>54.5</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F140">
+        <v>23.2946173276591</v>
+      </c>
+      <c r="G140">
+        <v>2.7286242778922301</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>4</v>
       </c>
@@ -3622,8 +4943,14 @@
       <c r="E141">
         <v>64.5</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F141">
+        <v>4.9440034428117201</v>
+      </c>
+      <c r="G141">
+        <v>0.57960507519119997</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>4</v>
       </c>
@@ -3639,8 +4966,14 @@
       <c r="E142">
         <v>59.5</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F142">
+        <v>7.0793258811773097</v>
+      </c>
+      <c r="G142">
+        <v>0.83005337783201705</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>4</v>
       </c>
@@ -3654,10 +4987,16 @@
         <v>109.93432998839501</v>
       </c>
       <c r="E143" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F143">
+        <v>3.2121540448720598</v>
+      </c>
+      <c r="G143">
+        <v>0.37875045414847203</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>4</v>
       </c>
@@ -3673,8 +5012,14 @@
       <c r="E144">
         <v>77.583330000000004</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F144">
+        <v>5.39559580288525</v>
+      </c>
+      <c r="G144">
+        <v>0.63300246321311504</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>4</v>
       </c>
@@ -3690,8 +5035,14 @@
       <c r="E145">
         <v>82.428566000000004</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F145">
+        <v>3.26864616971949</v>
+      </c>
+      <c r="G145">
+        <v>0.38441905585665798</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>4</v>
       </c>
@@ -3705,10 +5056,16 @@
         <v>26.240069084628701</v>
       </c>
       <c r="E146" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F146">
+        <v>28.718343999999998</v>
+      </c>
+      <c r="G146">
+        <v>3.3638710000000001</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>4</v>
       </c>
@@ -3724,8 +5081,14 @@
       <c r="E147">
         <v>53.444443</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F147">
+        <v>6.8263049940567697</v>
+      </c>
+      <c r="G147">
+        <v>0.79996634504480901</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>4</v>
       </c>
@@ -3739,10 +5102,16 @@
         <v>26.877923292797</v>
       </c>
       <c r="E148" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F148">
+        <v>11.7393258186813</v>
+      </c>
+      <c r="G148">
+        <v>1.37495953434066</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>4</v>
       </c>
@@ -3758,8 +5127,14 @@
       <c r="E149">
         <v>38</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F149">
+        <v>26.6214537160002</v>
+      </c>
+      <c r="G149">
+        <v>3.1182349370209699</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>4</v>
       </c>
@@ -3775,8 +5150,14 @@
       <c r="E150">
         <v>60.666668000000001</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F150">
+        <v>7.4236812422723499</v>
+      </c>
+      <c r="G150">
+        <v>0.87042518622946297</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -3792,8 +5173,14 @@
       <c r="E151">
         <v>40</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F151">
+        <v>12.221697909224901</v>
+      </c>
+      <c r="G151">
+        <v>1.4314340709304301</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>4</v>
       </c>
@@ -3809,8 +5196,14 @@
       <c r="E152">
         <v>42.523808000000002</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F152">
+        <v>1.11370662388325</v>
+      </c>
+      <c r="G152">
+        <v>0.13043437275736999</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>4</v>
       </c>
@@ -3824,10 +5217,16 @@
         <v>53.267397881996999</v>
       </c>
       <c r="E153" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F153">
+        <v>26.264923741178102</v>
+      </c>
+      <c r="G153">
+        <v>3.0765751647672701</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>4</v>
       </c>
@@ -3843,8 +5242,14 @@
       <c r="E154">
         <v>62.774192999999997</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F154">
+        <v>1.2155348887272299</v>
+      </c>
+      <c r="G154">
+        <v>0.14513149094877001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>4</v>
       </c>
@@ -3858,10 +5263,16 @@
         <v>17.247437185929599</v>
       </c>
       <c r="E155" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F155">
+        <v>6.5558167231482596</v>
+      </c>
+      <c r="G155">
+        <v>0.76793123950369702</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>4</v>
       </c>
@@ -3877,8 +5288,14 @@
       <c r="E156">
         <v>34</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F156">
+        <v>10.9674998093956</v>
+      </c>
+      <c r="G156">
+        <v>1.2850282773825501</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>4</v>
       </c>
@@ -3892,10 +5309,16 @@
         <v>32.729561067701503</v>
       </c>
       <c r="E157" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F157">
+        <v>5.9718426903181197</v>
+      </c>
+      <c r="G157">
+        <v>0.700379353726575</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>4</v>
       </c>
@@ -3911,8 +5334,14 @@
       <c r="E158">
         <v>13.909091</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F158">
+        <v>19.331165914755399</v>
+      </c>
+      <c r="G158">
+        <v>3.2968464234389501</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>4</v>
       </c>
@@ -3928,8 +5357,14 @@
       <c r="E159">
         <v>11.2952385</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F159">
+        <v>20.8642588198901</v>
+      </c>
+      <c r="G159">
+        <v>3.5576618464811198</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>4</v>
       </c>
@@ -3945,8 +5380,14 @@
       <c r="E160">
         <v>28.305554999999998</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F160">
+        <v>13.634292819775901</v>
+      </c>
+      <c r="G160">
+        <v>2.3266502171390901</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -3962,8 +5403,14 @@
       <c r="E161">
         <v>8.3333329999999997</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F161">
+        <v>4.3071130330950798</v>
+      </c>
+      <c r="G161">
+        <v>0.73492716234211297</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>4</v>
       </c>
@@ -3979,8 +5426,14 @@
       <c r="E162">
         <v>12.2</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F162">
+        <v>16.5205591130612</v>
+      </c>
+      <c r="G162">
+        <v>2.81888510918367</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>4</v>
       </c>
@@ -3994,10 +5447,16 @@
         <v>153.646870523319</v>
       </c>
       <c r="E163" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F163">
+        <v>14.510690599156099</v>
+      </c>
+      <c r="G163">
+        <v>2.4745425443037998</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>4</v>
       </c>
@@ -4013,8 +5472,14 @@
       <c r="E164">
         <v>16.27027</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F164">
+        <v>14.368860258646899</v>
+      </c>
+      <c r="G164">
+        <v>2.4513274029863301</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>4</v>
       </c>
@@ -4030,8 +5495,14 @@
       <c r="E165">
         <v>22.508772</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F165">
+        <v>16.743311743970299</v>
+      </c>
+      <c r="G165">
+        <v>2.8569221766739799</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>4</v>
       </c>
@@ -4047,8 +5518,14 @@
       <c r="E166">
         <v>12.754386</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F166">
+        <v>5.76377307257372</v>
+      </c>
+      <c r="G166">
+        <v>0.98915432364729405</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>4</v>
       </c>
@@ -4064,8 +5541,14 @@
       <c r="E167">
         <v>11.857143000000001</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F167">
+        <v>5.5525580375317096</v>
+      </c>
+      <c r="G167">
+        <v>0.94750232510224197</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>4</v>
       </c>
@@ -4081,8 +5564,14 @@
       <c r="E168">
         <v>10.412698000000001</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F168">
+        <v>14.0899168802178</v>
+      </c>
+      <c r="G168">
+        <v>2.4028212540834799</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>4</v>
       </c>
@@ -4098,8 +5587,14 @@
       <c r="E169">
         <v>13.409091</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F169">
+        <v>5.4913276410305203</v>
+      </c>
+      <c r="G169">
+        <v>0.93706470127863895</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>4</v>
       </c>
@@ -4115,8 +5610,14 @@
       <c r="E170">
         <v>20.428571999999999</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F170">
+        <v>8.7421671876852702</v>
+      </c>
+      <c r="G170">
+        <v>1.4911711137460799</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>4</v>
       </c>
@@ -4132,8 +5633,14 @@
       <c r="E171">
         <v>8.3809520000000006</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F171">
+        <v>4.3021078010527303</v>
+      </c>
+      <c r="G171">
+        <v>0.73407467014328898</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>4</v>
       </c>
@@ -4149,8 +5656,14 @@
       <c r="E172">
         <v>12.043479</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F172">
+        <v>12.2752863948058</v>
+      </c>
+      <c r="G172">
+        <v>2.0945385271064998</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>4</v>
       </c>
@@ -4166,8 +5679,14 @@
       <c r="E173">
         <v>20.416665999999999</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F173">
+        <v>8.7192742062671797</v>
+      </c>
+      <c r="G173">
+        <v>1.4874372046179201</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>4</v>
       </c>
@@ -4183,8 +5702,14 @@
       <c r="E174">
         <v>8.6923069999999996</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F174">
+        <v>9.4236729198981504</v>
+      </c>
+      <c r="G174">
+        <v>1.6073140684612599</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>4</v>
       </c>
@@ -4200,8 +5725,14 @@
       <c r="E175">
         <v>9.4347829999999995</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F175">
+        <v>4.7752482737100399</v>
+      </c>
+      <c r="G175">
+        <v>0.814948149428812</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>4</v>
       </c>
@@ -4217,8 +5748,14 @@
       <c r="E176">
         <v>10.283018999999999</v>
       </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F176">
+        <v>12.766333017751</v>
+      </c>
+      <c r="G176">
+        <v>2.1776262233322301</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>4</v>
       </c>
@@ -4234,8 +5771,14 @@
       <c r="E177">
         <v>8.1549289999999992</v>
       </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F177">
+        <v>13.218354053414799</v>
+      </c>
+      <c r="G177">
+        <v>2.2530159234653202</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>4</v>
       </c>
@@ -4251,8 +5794,14 @@
       <c r="E178">
         <v>7.6923069999999996</v>
       </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F178">
+        <v>13.2324357552561</v>
+      </c>
+      <c r="G178">
+        <v>2.2546456644951101</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>4</v>
       </c>
@@ -4266,10 +5815,16 @@
         <v>214.601403182155</v>
       </c>
       <c r="E179" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F179">
+        <v>12.473278306340699</v>
+      </c>
+      <c r="G179">
+        <v>2.1276821191749402</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>4</v>
       </c>
@@ -4285,8 +5840,14 @@
       <c r="E180">
         <v>91.166663999999997</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F180">
+        <v>5.5489030356973696</v>
+      </c>
+      <c r="G180">
+        <v>0.78047366120056805</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>4</v>
       </c>
@@ -4302,8 +5863,14 @@
       <c r="E181">
         <v>93.947370000000006</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F181">
+        <v>3.34865198642997</v>
+      </c>
+      <c r="G181">
+        <v>0.47154653947256098</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>4</v>
       </c>
@@ -4319,8 +5886,14 @@
       <c r="E182">
         <v>69.192310000000006</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F182">
+        <v>5.0440073667344496</v>
+      </c>
+      <c r="G182">
+        <v>0.71030912875152497</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>4</v>
       </c>
@@ -4336,8 +5909,14 @@
       <c r="E183">
         <v>47.294113000000003</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F183">
+        <v>6.32796184280632</v>
+      </c>
+      <c r="G183">
+        <v>0.89167517179614497</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>4</v>
       </c>
@@ -4353,8 +5932,14 @@
       <c r="E184">
         <v>28.382349999999999</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F184">
+        <v>14.672898652957899</v>
+      </c>
+      <c r="G184">
+        <v>2.0824279661499498</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>4</v>
       </c>
@@ -4370,8 +5955,14 @@
       <c r="E185">
         <v>31</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F185">
+        <v>12.9715898002959</v>
+      </c>
+      <c r="G185">
+        <v>1.8268793607618301</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>4</v>
       </c>
@@ -4387,8 +5978,14 @@
       <c r="E186">
         <v>30.352941999999999</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F186">
+        <v>5.8493116423381597</v>
+      </c>
+      <c r="G186">
+        <v>0.82325080028801501</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>4</v>
       </c>
@@ -4404,8 +6001,14 @@
       <c r="E187">
         <v>43.206898000000002</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F187">
+        <v>6.5773901236647099</v>
+      </c>
+      <c r="G187">
+        <v>0.92608809484168997</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>4</v>
       </c>
@@ -4421,8 +6024,14 @@
       <c r="E188">
         <v>23.788945999999999</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F188">
+        <v>6.5826590208393201</v>
+      </c>
+      <c r="G188">
+        <v>1.1231714780109201</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>4</v>
       </c>
@@ -4438,8 +6047,14 @@
       <c r="E189">
         <v>11.604255999999999</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F189">
+        <v>7.9630516185087101</v>
+      </c>
+      <c r="G189">
+        <v>1.35873540139658</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>4</v>
       </c>
@@ -4453,10 +6068,16 @@
         <v>118.710985630135</v>
       </c>
       <c r="E190" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F190">
+        <v>20.906000988356201</v>
+      </c>
+      <c r="G190">
+        <v>3.5669045109589002</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>4</v>
       </c>
@@ -4472,8 +6093,14 @@
       <c r="E191">
         <v>17.153255000000001</v>
       </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F191">
+        <v>21.265871626004699</v>
+      </c>
+      <c r="G191">
+        <v>3.6297042068557901</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>4</v>
       </c>
@@ -4489,8 +6116,14 @@
       <c r="E192">
         <v>9.2360249999999997</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F192">
+        <v>9.6566016747321104</v>
+      </c>
+      <c r="G192">
+        <v>1.64735686519184</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>4</v>
       </c>
@@ -4506,8 +6139,14 @@
       <c r="E193">
         <v>11.757142999999999</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F193">
+        <v>9.2076567466750507</v>
+      </c>
+      <c r="G193">
+        <v>1.5658526338066101</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>4</v>
       </c>
@@ -4523,8 +6162,14 @@
       <c r="E194">
         <v>9.8486840000000004</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F194">
+        <v>9.3918951007284601</v>
+      </c>
+      <c r="G194">
+        <v>1.60255102511932</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>4</v>
       </c>
@@ -4540,8 +6185,14 @@
       <c r="E195">
         <v>4.125</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F195">
+        <v>7.9840722283272303</v>
+      </c>
+      <c r="G195">
+        <v>1.1089419504273501</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>4</v>
       </c>
@@ -4557,8 +6208,14 @@
       <c r="E196">
         <v>6.5555553</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F196">
+        <v>6.6675269939059598</v>
+      </c>
+      <c r="G196">
+        <v>0.92822882923856598</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>4</v>
       </c>
@@ -4574,8 +6231,14 @@
       <c r="E197">
         <v>5</v>
       </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F197">
+        <v>7.9761499367311099</v>
+      </c>
+      <c r="G197">
+        <v>1.106860771529</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>4</v>
       </c>
@@ -4589,10 +6252,16 @@
         <v>201.706350134487</v>
       </c>
       <c r="E198" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F198">
+        <v>8.8997626724086292</v>
+      </c>
+      <c r="G198">
+        <v>1.2367541686638699</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>4</v>
       </c>
@@ -4608,8 +6277,14 @@
       <c r="E199">
         <v>5.4285717</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F199">
+        <v>9.0441757984265703</v>
+      </c>
+      <c r="G199">
+        <v>1.2548455959790199</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>4</v>
       </c>
@@ -4625,8 +6300,14 @@
       <c r="E200">
         <v>3.7692307999999999</v>
       </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F200">
+        <v>8.0808127210173293</v>
+      </c>
+      <c r="G200">
+        <v>1.1325088750979899</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>4</v>
       </c>
@@ -4642,8 +6323,14 @@
       <c r="E201">
         <v>3.6296295999999999</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F201">
+        <v>17.071665894125399</v>
+      </c>
+      <c r="G201">
+        <v>2.3732202704954002</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>4</v>
       </c>
@@ -4659,8 +6346,14 @@
       <c r="E202">
         <v>4.3684206000000003</v>
       </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F202">
+        <v>17.061747293263601</v>
+      </c>
+      <c r="G202">
+        <v>2.37208603832753</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>4</v>
       </c>
@@ -4676,8 +6369,14 @@
       <c r="E203">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F203">
+        <v>8.4481968370502099</v>
+      </c>
+      <c r="G203">
+        <v>1.17212438144753</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>4</v>
       </c>
@@ -4693,8 +6392,14 @@
       <c r="E204">
         <v>4.08</v>
       </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F204">
+        <v>9.6681252092210404</v>
+      </c>
+      <c r="G204">
+        <v>1.3491844351697699</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>4</v>
       </c>
@@ -4710,8 +6415,14 @@
       <c r="E205">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F205">
+        <v>16.082912837193</v>
+      </c>
+      <c r="G205">
+        <v>2.2464038477193</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>4</v>
       </c>
@@ -4727,8 +6438,14 @@
       <c r="E206">
         <v>3.8000001999999999</v>
       </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F206">
+        <v>8.7661154271087298</v>
+      </c>
+      <c r="G206">
+        <v>1.21989262237933</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>4</v>
       </c>
@@ -4744,8 +6461,14 @@
       <c r="E207">
         <v>3.25</v>
       </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F207">
+        <v>7.7110019706843902</v>
+      </c>
+      <c r="G207">
+        <v>1.0708013877506499</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>4</v>
       </c>
@@ -4761,8 +6484,14 @@
       <c r="E208">
         <v>6.7857146000000004</v>
       </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F208">
+        <v>8.8110653964265797</v>
+      </c>
+      <c r="G208">
+        <v>1.2255795643030001</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>4</v>
       </c>
@@ -4776,10 +6505,16 @@
         <v>233.46657081236501</v>
       </c>
       <c r="E209" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F209">
+        <v>7.8377901472245401</v>
+      </c>
+      <c r="G209">
+        <v>1.08918386592237</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>4</v>
       </c>
@@ -4795,8 +6530,14 @@
       <c r="E210">
         <v>8</v>
       </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F210">
+        <v>6.6975304722843099</v>
+      </c>
+      <c r="G210">
+        <v>0.93320000916405899</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>4</v>
       </c>
@@ -4812,8 +6553,14 @@
       <c r="E211">
         <v>8.6578949999999999</v>
       </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F211">
+        <v>10.488198072024201</v>
+      </c>
+      <c r="G211">
+        <v>1.46093344442408</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>4</v>
       </c>
@@ -4829,8 +6576,14 @@
       <c r="E212">
         <v>6.8461537000000003</v>
       </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F212">
+        <v>14.2039655155217</v>
+      </c>
+      <c r="G212">
+        <v>1.98734506268776</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>4</v>
       </c>
@@ -4846,8 +6599,14 @@
       <c r="E213">
         <v>14</v>
       </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F213">
+        <v>7.3089486619965003</v>
+      </c>
+      <c r="G213">
+        <v>1.01915984522767</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>4</v>
       </c>
@@ -4863,8 +6622,14 @@
       <c r="E214">
         <v>9.6153849999999998</v>
       </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F214">
+        <v>6.67853612665178</v>
+      </c>
+      <c r="G214">
+        <v>0.93059260683044898</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>4</v>
       </c>
@@ -4880,8 +6645,14 @@
       <c r="E215">
         <v>9.3846150000000002</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F215">
+        <v>7.6474745287214301</v>
+      </c>
+      <c r="G215">
+        <v>1.0665325067943201</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>4</v>
       </c>
@@ -4897,8 +6668,14 @@
       <c r="E216">
         <v>5.2787879999999996</v>
       </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F216">
+        <v>11.1024813426537</v>
+      </c>
+      <c r="G216">
+        <v>1.54888552545503</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>4</v>
       </c>
@@ -4914,8 +6691,14 @@
       <c r="E217">
         <v>5.28125</v>
       </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F217">
+        <v>7.7686601246601903</v>
+      </c>
+      <c r="G217">
+        <v>1.0913918636893201</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>4</v>
       </c>
@@ -4931,8 +6714,14 @@
       <c r="E218">
         <v>9.4615369999999999</v>
       </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F218">
+        <v>16.7525221025689</v>
+      </c>
+      <c r="G218">
+        <v>2.3409484680292501</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>4</v>
       </c>
@@ -4948,8 +6737,14 @@
       <c r="E219">
         <v>9.6111109999999993</v>
       </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F219">
+        <v>4.4401637834716201</v>
+      </c>
+      <c r="G219">
+        <v>0.61989636249585101</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>4</v>
       </c>
@@ -4965,8 +6760,14 @@
       <c r="E220">
         <v>10.510204</v>
       </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F220">
+        <v>8.0417349998661294</v>
+      </c>
+      <c r="G220">
+        <v>1.1229265216867499</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>4</v>
       </c>
@@ -4982,8 +6783,14 @@
       <c r="E221">
         <v>77.230773999999997</v>
       </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F221">
+        <v>3.5490407508975199</v>
+      </c>
+      <c r="G221">
+        <v>0.49843000122388997</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>4</v>
       </c>
@@ -4999,8 +6806,14 @@
       <c r="E222">
         <v>81.777780000000007</v>
       </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F222">
+        <v>9.5649872916066307</v>
+      </c>
+      <c r="G222">
+        <v>1.34313561503362</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>4</v>
       </c>
@@ -5016,8 +6829,14 @@
       <c r="E223">
         <v>77.444434999999999</v>
       </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F223">
+        <v>3.0625811356991801</v>
+      </c>
+      <c r="G223">
+        <v>0.42991368198951901</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>4</v>
       </c>
@@ -5033,8 +6852,14 @@
       <c r="E224">
         <v>83.55556</v>
       </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F224">
+        <v>4.4619154972255703</v>
+      </c>
+      <c r="G224">
+        <v>0.62485114161640498</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>4</v>
       </c>
@@ -5050,8 +6875,14 @@
       <c r="E225">
         <v>65.63158</v>
       </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F225">
+        <v>4.36395931017534</v>
+      </c>
+      <c r="G225">
+        <v>0.61167755941715796</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>4</v>
       </c>
@@ -5065,10 +6896,16 @@
         <v>0.72075736844051597</v>
       </c>
       <c r="E226" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F226">
+        <v>3.46517511756202</v>
+      </c>
+      <c r="G226">
+        <v>0.485863159949112</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>4</v>
       </c>
@@ -5084,8 +6921,14 @@
       <c r="E227">
         <v>70.086950000000002</v>
       </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F227">
+        <v>2.5523210961571499</v>
+      </c>
+      <c r="G227">
+        <v>0.35809197602091702</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>4</v>
       </c>
@@ -5101,8 +6944,14 @@
       <c r="E228">
         <v>62.000003999999997</v>
       </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F228">
+        <v>6.1090581216160098</v>
+      </c>
+      <c r="G228">
+        <v>0.85738900018447595</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>4</v>
       </c>
@@ -5118,8 +6967,14 @@
       <c r="E229">
         <v>76.87097</v>
       </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F229">
+        <v>4.79168979990287</v>
+      </c>
+      <c r="G229">
+        <v>0.67265330981868199</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>4</v>
       </c>
@@ -5135,8 +6990,14 @@
       <c r="E230">
         <v>103.82608999999999</v>
       </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F230">
+        <v>9.6760610347695799</v>
+      </c>
+      <c r="G230">
+        <v>1.35872875207943</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>4</v>
       </c>
@@ -5152,8 +7013,14 @@
       <c r="E231">
         <v>26.555554999999998</v>
       </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F231">
+        <v>3.4232730893076702</v>
+      </c>
+      <c r="G231">
+        <v>0.47999774769834103</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>4</v>
       </c>
@@ -5169,8 +7036,14 @@
       <c r="E232">
         <v>56.933329999999998</v>
       </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F232">
+        <v>2.9137502641792699</v>
+      </c>
+      <c r="G232">
+        <v>0.40860832646432699</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>4</v>
       </c>
@@ -5186,8 +7059,14 @@
       <c r="E233">
         <v>26.714283000000002</v>
       </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F233">
+        <v>4.4954311183968398</v>
+      </c>
+      <c r="G233">
+        <v>0.58021189255989003</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>4</v>
       </c>
@@ -5203,8 +7082,14 @@
       <c r="E234">
         <v>71.125</v>
       </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F234">
+        <v>4.3593073717379998</v>
+      </c>
+      <c r="G234">
+        <v>0.61191662604384101</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>4</v>
       </c>
@@ -5220,8 +7105,14 @@
       <c r="E235">
         <v>63.166663999999997</v>
       </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F235">
+        <v>4.3763499140519704</v>
+      </c>
+      <c r="G235">
+        <v>0.61426985332049999</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>4</v>
       </c>
@@ -5237,8 +7128,14 @@
       <c r="E236">
         <v>72.054060000000007</v>
       </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F236">
+        <v>2.5496178144966901</v>
+      </c>
+      <c r="G236">
+        <v>0.35744553102020599</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>4</v>
       </c>
@@ -5254,8 +7151,14 @@
       <c r="E237">
         <v>76.714280000000002</v>
       </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F237">
+        <v>4.1602885069341102</v>
+      </c>
+      <c r="G237">
+        <v>0.583745668259813</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>4</v>
       </c>
@@ -5271,8 +7174,14 @@
       <c r="E238">
         <v>40.571429999999999</v>
       </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F238">
+        <v>2.9978411289241498</v>
+      </c>
+      <c r="G238">
+        <v>0.41817747024323798</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>4</v>
       </c>
@@ -5288,8 +7197,14 @@
       <c r="E239">
         <v>128.83332999999999</v>
       </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F239">
+        <v>5.8381266365861899</v>
+      </c>
+      <c r="G239">
+        <v>0.81850410291364695</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>4</v>
       </c>
@@ -5305,8 +7220,14 @@
       <c r="E240">
         <v>121.16665999999999</v>
       </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F240">
+        <v>19.318314301091501</v>
+      </c>
+      <c r="G240">
+        <v>2.7092574626364399</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>4</v>
       </c>
@@ -5322,8 +7243,14 @@
       <c r="E241">
         <v>230.11111</v>
       </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F241">
+        <v>6.5093429873551099</v>
+      </c>
+      <c r="G241">
+        <v>0.91273350825430299</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>4</v>
       </c>
@@ -5339,8 +7266,14 @@
       <c r="E242">
         <v>242.54544000000001</v>
       </c>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F242">
+        <v>11.025523281308899</v>
+      </c>
+      <c r="G242">
+        <v>1.54913649454629</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>4</v>
       </c>
@@ -5356,8 +7289,14 @@
       <c r="E243">
         <v>165.19998000000001</v>
       </c>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F243">
+        <v>7.3600155029259904</v>
+      </c>
+      <c r="G243">
+        <v>1.03279014010327</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>4</v>
       </c>
@@ -5373,8 +7312,14 @@
       <c r="E244">
         <v>214.86109999999999</v>
       </c>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F244">
+        <v>5.1106529571459003</v>
+      </c>
+      <c r="G244">
+        <v>0.716837020310506</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>4</v>
       </c>
@@ -5390,8 +7335,14 @@
       <c r="E245">
         <v>199.60714999999999</v>
       </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F245">
+        <v>8.1735003696957698</v>
+      </c>
+      <c r="G245">
+        <v>1.1470914621569299</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>4</v>
       </c>
@@ -5405,10 +7356,16 @@
         <v>31.835617798967</v>
       </c>
       <c r="E246" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F246">
+        <v>19.380357367896501</v>
+      </c>
+      <c r="G246">
+        <v>2.7179553102143799</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>4</v>
       </c>
@@ -5424,8 +7381,14 @@
       <c r="E247">
         <v>119.66667</v>
       </c>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F247">
+        <v>20.889411729117299</v>
+      </c>
+      <c r="G247">
+        <v>2.9285949638759798</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>4</v>
       </c>
@@ -5441,8 +7404,14 @@
       <c r="E248">
         <v>202.09676999999999</v>
       </c>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F248">
+        <v>4.0907739245083397</v>
+      </c>
+      <c r="G248">
+        <v>0.57434076727412597</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>4</v>
       </c>
@@ -5458,8 +7427,14 @@
       <c r="E249">
         <v>174.47540000000001</v>
       </c>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F249">
+        <v>8.48444887099296</v>
+      </c>
+      <c r="G249">
+        <v>1.1912251404222001</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>4</v>
       </c>
@@ -5475,8 +7450,14 @@
       <c r="E250">
         <v>151.23077000000001</v>
       </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F250">
+        <v>7.6207872927646498</v>
+      </c>
+      <c r="G250">
+        <v>1.07019102933985</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>4</v>
       </c>
@@ -5492,8 +7473,14 @@
       <c r="E251">
         <v>172.45652999999999</v>
       </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F251">
+        <v>8.6315762675941698</v>
+      </c>
+      <c r="G251">
+        <v>1.21192501244813</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>4</v>
       </c>
@@ -5509,8 +7496,14 @@
       <c r="E252">
         <v>171.9434</v>
       </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F252">
+        <v>7.1821622706341497</v>
+      </c>
+      <c r="G252">
+        <v>1.0083026484878099</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>4</v>
       </c>
@@ -5526,8 +7519,14 @@
       <c r="E253">
         <v>174.67058</v>
       </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F253">
+        <v>10.5345543701309</v>
+      </c>
+      <c r="G253">
+        <v>1.47941388984387</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>4</v>
       </c>
@@ -5543,8 +7542,14 @@
       <c r="E254">
         <v>123.68965</v>
       </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F254">
+        <v>13.6159074514905</v>
+      </c>
+      <c r="G254">
+        <v>1.91232708590786</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>4</v>
       </c>
@@ -5560,8 +7565,14 @@
       <c r="E255">
         <v>117.414635</v>
       </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F255">
+        <v>13.4848023856793</v>
+      </c>
+      <c r="G255">
+        <v>1.8945366232492999</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>4</v>
       </c>
@@ -5577,8 +7588,14 @@
       <c r="E256">
         <v>131.03702999999999</v>
       </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F256">
+        <v>24.4503730370112</v>
+      </c>
+      <c r="G256">
+        <v>3.4264097664106101</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>4</v>
       </c>
@@ -5594,8 +7611,14 @@
       <c r="E257">
         <v>122.80953</v>
       </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F257">
+        <v>12.584550175855099</v>
+      </c>
+      <c r="G257">
+        <v>1.76636909597586</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>4</v>
       </c>
@@ -5611,8 +7634,14 @@
       <c r="E258">
         <v>132.45651000000001</v>
       </c>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F258">
+        <v>12.6430489952897</v>
+      </c>
+      <c r="G258">
+        <v>1.7747111801695701</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>4</v>
       </c>
@@ -5628,8 +7657,14 @@
       <c r="E259">
         <v>133.75</v>
       </c>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F259">
+        <v>14.676507069504201</v>
+      </c>
+      <c r="G259">
+        <v>2.0616199121632399</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>4</v>
       </c>
@@ -5645,8 +7680,14 @@
       <c r="E260">
         <v>111.16128500000001</v>
       </c>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F260">
+        <v>16.645357677518</v>
+      </c>
+      <c r="G260">
+        <v>2.3357582184837198</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>4</v>
       </c>
@@ -5662,11 +7703,1647 @@
       <c r="E261">
         <v>143.83332999999999</v>
       </c>
+      <c r="F261">
+        <v>10.9538504624573</v>
+      </c>
+      <c r="G261">
+        <v>1.5381558609215</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>269</v>
+      </c>
+      <c r="C262" t="s">
+        <v>277</v>
+      </c>
+      <c r="D262">
+        <v>306.76684165335899</v>
+      </c>
+      <c r="E262">
+        <v>339.04079999999999</v>
+      </c>
+      <c r="F262">
+        <v>7.4557542909390699</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>269</v>
+      </c>
+      <c r="C263" t="s">
+        <v>409</v>
+      </c>
+      <c r="D263">
+        <v>288.78563672424701</v>
+      </c>
+      <c r="E263">
+        <v>424.43669999999997</v>
+      </c>
+      <c r="F263">
+        <v>10.2087644883834</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>269</v>
+      </c>
+      <c r="C264" t="s">
+        <v>410</v>
+      </c>
+      <c r="D264">
+        <v>344.13902733292201</v>
+      </c>
+      <c r="E264">
+        <v>314.09692000000001</v>
+      </c>
+      <c r="F264">
+        <v>7.8354947019446799</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>269</v>
+      </c>
+      <c r="C265" t="s">
+        <v>411</v>
+      </c>
+      <c r="D265">
+        <v>291.00200268675098</v>
+      </c>
+      <c r="E265">
+        <v>271.91356999999999</v>
+      </c>
+      <c r="F265">
+        <v>9.6770793711441598</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>269</v>
+      </c>
+      <c r="C266" t="s">
+        <v>412</v>
+      </c>
+      <c r="D266">
+        <v>297.49832594593602</v>
+      </c>
+      <c r="E266">
+        <v>339.88596000000001</v>
+      </c>
+      <c r="F266">
+        <v>9.5356840945225603</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>269</v>
+      </c>
+      <c r="C267" t="s">
+        <v>413</v>
+      </c>
+      <c r="D267">
+        <v>281.046416194485</v>
+      </c>
+      <c r="E267">
+        <v>284.13711999999998</v>
+      </c>
+      <c r="F267">
+        <v>11.696150834493199</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>269</v>
+      </c>
+      <c r="C268" t="s">
+        <v>414</v>
+      </c>
+      <c r="D268">
+        <v>284.97317367441002</v>
+      </c>
+      <c r="E268">
+        <v>268.68180000000001</v>
+      </c>
+      <c r="F268">
+        <v>9.4281931741278306</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>269</v>
+      </c>
+      <c r="C269" t="s">
+        <v>294</v>
+      </c>
+      <c r="D269">
+        <v>312.04458024008301</v>
+      </c>
+      <c r="E269">
+        <v>564.56524999999999</v>
+      </c>
+      <c r="F269">
+        <v>12.269904550235101</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>269</v>
+      </c>
+      <c r="C270" t="s">
+        <v>295</v>
+      </c>
+      <c r="D270">
+        <v>395.23046318306399</v>
+      </c>
+      <c r="E270">
+        <v>519.60829999999999</v>
+      </c>
+      <c r="F270">
+        <v>18.894608730078499</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>269</v>
+      </c>
+      <c r="C271" t="s">
+        <v>281</v>
+      </c>
+      <c r="D271">
+        <v>255.06126142526</v>
+      </c>
+      <c r="E271">
+        <v>388.23334</v>
+      </c>
+      <c r="F271">
+        <v>10.3993419500539</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>269</v>
+      </c>
+      <c r="C272" t="s">
+        <v>282</v>
+      </c>
+      <c r="D272">
+        <v>258.249229577888</v>
+      </c>
+      <c r="E272">
+        <v>377.65532999999999</v>
+      </c>
+      <c r="F272">
+        <v>10.1031003270128</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>269</v>
+      </c>
+      <c r="C273" t="s">
+        <v>283</v>
+      </c>
+      <c r="D273">
+        <v>305.88113996147803</v>
+      </c>
+      <c r="E273">
+        <v>362.88170000000002</v>
+      </c>
+      <c r="F273">
+        <v>10.751757334608801</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>269</v>
+      </c>
+      <c r="C274" t="s">
+        <v>278</v>
+      </c>
+      <c r="D274">
+        <v>333.24142921396998</v>
+      </c>
+      <c r="E274">
+        <v>199.36564999999999</v>
+      </c>
+      <c r="F274">
+        <v>17.0636141920852</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>269</v>
+      </c>
+      <c r="C275" t="s">
+        <v>279</v>
+      </c>
+      <c r="D275">
+        <v>299.680547930199</v>
+      </c>
+      <c r="E275">
+        <v>275.9434</v>
+      </c>
+      <c r="F275">
+        <v>13.313729538158</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>269</v>
+      </c>
+      <c r="C276" t="s">
+        <v>280</v>
+      </c>
+      <c r="D276">
+        <v>313.03303426464203</v>
+      </c>
+      <c r="E276">
+        <v>247.20514</v>
+      </c>
+      <c r="F276">
+        <v>26.0341466894406</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>269</v>
+      </c>
+      <c r="C277" t="s">
+        <v>284</v>
+      </c>
+      <c r="D277">
+        <v>311.45544190052999</v>
+      </c>
+      <c r="E277">
+        <v>346.66665999999998</v>
+      </c>
+      <c r="F277">
+        <v>11.613919995984</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>269</v>
+      </c>
+      <c r="C278" t="s">
+        <v>285</v>
+      </c>
+      <c r="D278">
+        <v>281.06337907221302</v>
+      </c>
+      <c r="E278">
+        <v>340.0351</v>
+      </c>
+      <c r="F278">
+        <v>12.919463252227301</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>269</v>
+      </c>
+      <c r="C279" t="s">
+        <v>286</v>
+      </c>
+      <c r="D279">
+        <v>308.01284844593499</v>
+      </c>
+      <c r="E279">
+        <v>439.14654999999999</v>
+      </c>
+      <c r="F279">
+        <v>13.6850245685799</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>269</v>
+      </c>
+      <c r="C280" t="s">
+        <v>287</v>
+      </c>
+      <c r="D280">
+        <v>326.64861046067801</v>
+      </c>
+      <c r="E280">
+        <v>416.0471</v>
+      </c>
+      <c r="F280">
+        <v>15.8205921850567</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>269</v>
+      </c>
+      <c r="C281" t="s">
+        <v>288</v>
+      </c>
+      <c r="D281">
+        <v>309.52296441309198</v>
+      </c>
+      <c r="E281">
+        <v>371.08069999999998</v>
+      </c>
+      <c r="F281">
+        <v>11.629407837931801</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>269</v>
+      </c>
+      <c r="C282" t="s">
+        <v>289</v>
+      </c>
+      <c r="D282">
+        <v>282.55072942578801</v>
+      </c>
+      <c r="E282">
+        <v>412.3125</v>
+      </c>
+      <c r="F282">
+        <v>10.0679841331386</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>269</v>
+      </c>
+      <c r="C283" t="s">
+        <v>290</v>
+      </c>
+      <c r="D283">
+        <v>277.64634215602302</v>
+      </c>
+      <c r="E283">
+        <v>383.02258</v>
+      </c>
+      <c r="F283">
+        <v>11.318589884503799</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>269</v>
+      </c>
+      <c r="C284" t="s">
+        <v>415</v>
+      </c>
+      <c r="D284">
+        <v>283.16762882305102</v>
+      </c>
+      <c r="E284">
+        <v>318.55095999999998</v>
+      </c>
+      <c r="F284">
+        <v>8.2176502503872602</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>269</v>
+      </c>
+      <c r="C285" t="s">
+        <v>416</v>
+      </c>
+      <c r="D285">
+        <v>281.28016517591902</v>
+      </c>
+      <c r="E285">
+        <v>380.64834999999999</v>
+      </c>
+      <c r="F285">
+        <v>8.65989079555799</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>269</v>
+      </c>
+      <c r="C286" t="s">
+        <v>417</v>
+      </c>
+      <c r="D286">
+        <v>273.59511369815402</v>
+      </c>
+      <c r="E286">
+        <v>322.19412</v>
+      </c>
+      <c r="F286">
+        <v>10.262956688930201</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>269</v>
+      </c>
+      <c r="C287" t="s">
+        <v>418</v>
+      </c>
+      <c r="D287">
+        <v>205.72555036275</v>
+      </c>
+      <c r="E287">
+        <v>407.83629999999999</v>
+      </c>
+      <c r="F287">
+        <v>17.9643822918346</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>269</v>
+      </c>
+      <c r="C288" t="s">
+        <v>419</v>
+      </c>
+      <c r="D288">
+        <v>260.02856043731902</v>
+      </c>
+      <c r="E288">
+        <v>412.45596</v>
+      </c>
+      <c r="F288">
+        <v>7.7052029617662203</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>269</v>
+      </c>
+      <c r="C289" t="s">
+        <v>274</v>
+      </c>
+      <c r="D289">
+        <v>349.04997040252601</v>
+      </c>
+      <c r="E289">
+        <v>473.46154999999999</v>
+      </c>
+      <c r="F289">
+        <v>13.660494513862901</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>269</v>
+      </c>
+      <c r="C290" t="s">
+        <v>275</v>
+      </c>
+      <c r="D290">
+        <v>403.21865813254999</v>
+      </c>
+      <c r="E290">
+        <v>449.45519999999999</v>
+      </c>
+      <c r="F290">
+        <v>15.959723597751401</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>269</v>
+      </c>
+      <c r="C291" t="s">
+        <v>276</v>
+      </c>
+      <c r="D291">
+        <v>310.27120669597701</v>
+      </c>
+      <c r="E291">
+        <v>490.8913</v>
+      </c>
+      <c r="F291">
+        <v>7.3525066667105596</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>269</v>
+      </c>
+      <c r="C292" t="s">
+        <v>296</v>
+      </c>
+      <c r="D292">
+        <v>323.05716203268298</v>
+      </c>
+      <c r="E292">
+        <v>188.57480000000001</v>
+      </c>
+      <c r="F292">
+        <v>11.808746362685101</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>269</v>
+      </c>
+      <c r="C293" t="s">
+        <v>297</v>
+      </c>
+      <c r="D293">
+        <v>313.94401931454399</v>
+      </c>
+      <c r="E293">
+        <v>263.07873999999998</v>
+      </c>
+      <c r="F293">
+        <v>8.5390354079845192</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>269</v>
+      </c>
+      <c r="C294" t="s">
+        <v>298</v>
+      </c>
+      <c r="D294">
+        <v>318.19342513476198</v>
+      </c>
+      <c r="E294">
+        <v>240.05726999999999</v>
+      </c>
+      <c r="F294">
+        <v>19.606661171731801</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>269</v>
+      </c>
+      <c r="C295" t="s">
+        <v>299</v>
+      </c>
+      <c r="D295">
+        <v>321.210224213</v>
+      </c>
+      <c r="E295">
+        <v>234.30302</v>
+      </c>
+      <c r="F295">
+        <v>15.779844722289999</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>269</v>
+      </c>
+      <c r="C296" t="s">
+        <v>292</v>
+      </c>
+      <c r="D296">
+        <v>293.68772029363402</v>
+      </c>
+      <c r="E296">
+        <v>343.79860000000002</v>
+      </c>
+      <c r="F296">
+        <v>12.897050823260299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>269</v>
+      </c>
+      <c r="C297" t="s">
+        <v>293</v>
+      </c>
+      <c r="D297">
+        <v>326.07794006286201</v>
+      </c>
+      <c r="E297">
+        <v>310.76785000000001</v>
+      </c>
+      <c r="F297">
+        <v>7.4472211185770796</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>269</v>
+      </c>
+      <c r="C298" t="s">
+        <v>291</v>
+      </c>
+      <c r="D298">
+        <v>300.64784753014402</v>
+      </c>
+      <c r="E298">
+        <v>309.02246000000002</v>
+      </c>
+      <c r="F298">
+        <v>8.3561672415102599</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>269</v>
+      </c>
+      <c r="C299" t="s">
+        <v>420</v>
+      </c>
+      <c r="D299">
+        <v>283.31745766569099</v>
+      </c>
+      <c r="E299">
+        <v>114.59090399999999</v>
+      </c>
+      <c r="F299">
+        <v>12.5288813192993</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>269</v>
+      </c>
+      <c r="C300" t="s">
+        <v>421</v>
+      </c>
+      <c r="D300">
+        <v>290.57159954976299</v>
+      </c>
+      <c r="E300">
+        <v>196.33179999999999</v>
+      </c>
+      <c r="F300">
+        <v>13.854288067815901</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>269</v>
+      </c>
+      <c r="C301" t="s">
+        <v>422</v>
+      </c>
+      <c r="D301">
+        <v>306.40843141563698</v>
+      </c>
+      <c r="E301">
+        <v>148.10901000000001</v>
+      </c>
+      <c r="F301">
+        <v>7.9993070657864296</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>269</v>
+      </c>
+      <c r="C302" t="s">
+        <v>423</v>
+      </c>
+      <c r="D302">
+        <v>267.60360520843199</v>
+      </c>
+      <c r="E302">
+        <v>252.43540999999999</v>
+      </c>
+      <c r="F302">
+        <v>16.935865378230602</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>269</v>
+      </c>
+      <c r="C303" t="s">
+        <v>270</v>
+      </c>
+      <c r="D303">
+        <v>301.39304812017701</v>
+      </c>
+      <c r="E303">
+        <v>581.84780000000001</v>
+      </c>
+      <c r="F303">
+        <v>12.3357751414791</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>269</v>
+      </c>
+      <c r="C304" t="s">
+        <v>271</v>
+      </c>
+      <c r="D304">
+        <v>284.36878062702698</v>
+      </c>
+      <c r="E304">
+        <v>543.09090000000003</v>
+      </c>
+      <c r="F304">
+        <v>9.8590107400278395</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>269</v>
+      </c>
+      <c r="C305" t="s">
+        <v>272</v>
+      </c>
+      <c r="D305">
+        <v>284.01241817596502</v>
+      </c>
+      <c r="E305">
+        <v>587.4316</v>
+      </c>
+      <c r="F305">
+        <v>12.5974618538109</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>269</v>
+      </c>
+      <c r="C306" t="s">
+        <v>273</v>
+      </c>
+      <c r="D306">
+        <v>329.65638282062702</v>
+      </c>
+      <c r="E306">
+        <v>602.13995</v>
+      </c>
+      <c r="F306">
+        <v>10.673469078157099</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>408</v>
+      </c>
+      <c r="C307" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>408</v>
+      </c>
+      <c r="C308" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>408</v>
+      </c>
+      <c r="C309" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>408</v>
+      </c>
+      <c r="C310" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>408</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>408</v>
+      </c>
+      <c r="C312" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>408</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>408</v>
+      </c>
+      <c r="C314" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>408</v>
+      </c>
+      <c r="C315" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>408</v>
+      </c>
+      <c r="C316" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>408</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>408</v>
+      </c>
+      <c r="C318" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>408</v>
+      </c>
+      <c r="C319" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>408</v>
+      </c>
+      <c r="C320" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>408</v>
+      </c>
+      <c r="C321" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>408</v>
+      </c>
+      <c r="C322" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>408</v>
+      </c>
+      <c r="C323" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>408</v>
+      </c>
+      <c r="C324" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>408</v>
+      </c>
+      <c r="C325" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>408</v>
+      </c>
+      <c r="C326" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>408</v>
+      </c>
+      <c r="C327" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>408</v>
+      </c>
+      <c r="C328" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C329" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>408</v>
+      </c>
+      <c r="C330" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C331" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>408</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>408</v>
+      </c>
+      <c r="C333" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>408</v>
+      </c>
+      <c r="C334" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>408</v>
+      </c>
+      <c r="C335" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>408</v>
+      </c>
+      <c r="C336" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>408</v>
+      </c>
+      <c r="C337" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>408</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>408</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>408</v>
+      </c>
+      <c r="C340" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>408</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>408</v>
+      </c>
+      <c r="C342" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>408</v>
+      </c>
+      <c r="C343" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>408</v>
+      </c>
+      <c r="C344" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>408</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>408</v>
+      </c>
+      <c r="C346" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>408</v>
+      </c>
+      <c r="C347" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>408</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>408</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>408</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>408</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>408</v>
+      </c>
+      <c r="C352" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>408</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>408</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>408</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>408</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>408</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>408</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>408</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>408</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>408</v>
+      </c>
+      <c r="C361" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>408</v>
+      </c>
+      <c r="C362" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>408</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>408</v>
+      </c>
+      <c r="C364" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>408</v>
+      </c>
+      <c r="C365" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>408</v>
+      </c>
+      <c r="C366" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>408</v>
+      </c>
+      <c r="C367" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>408</v>
+      </c>
+      <c r="C368" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>408</v>
+      </c>
+      <c r="C369" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>408</v>
+      </c>
+      <c r="C370" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>408</v>
+      </c>
+      <c r="C371" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>408</v>
+      </c>
+      <c r="C372" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>408</v>
+      </c>
+      <c r="C373" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>408</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>408</v>
+      </c>
+      <c r="C375" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>408</v>
+      </c>
+      <c r="C376" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>408</v>
+      </c>
+      <c r="C377" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>408</v>
+      </c>
+      <c r="C378" s="3" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>408</v>
+      </c>
+      <c r="C379" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>408</v>
+      </c>
+      <c r="C380" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>408</v>
+      </c>
+      <c r="C381" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>408</v>
+      </c>
+      <c r="C382" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>408</v>
+      </c>
+      <c r="C383" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>408</v>
+      </c>
+      <c r="C384" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>408</v>
+      </c>
+      <c r="C385" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>408</v>
+      </c>
+      <c r="C386" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>408</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>408</v>
+      </c>
+      <c r="C388" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>408</v>
+      </c>
+      <c r="C389" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>408</v>
+      </c>
+      <c r="C390" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>408</v>
+      </c>
+      <c r="C391" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>408</v>
+      </c>
+      <c r="C392" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>408</v>
+      </c>
+      <c r="C393" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>408</v>
+      </c>
+      <c r="C394" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>408</v>
+      </c>
+      <c r="C395" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>408</v>
+      </c>
+      <c r="C396" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>408</v>
+      </c>
+      <c r="C397" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>408</v>
+      </c>
+      <c r="C398" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>408</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>408</v>
+      </c>
+      <c r="C400" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>408</v>
+      </c>
+      <c r="C401" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>408</v>
+      </c>
+      <c r="C402" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>408</v>
+      </c>
+      <c r="C403" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>408</v>
+      </c>
+      <c r="C404" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>408</v>
+      </c>
+      <c r="C405" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>408</v>
+      </c>
+      <c r="C406" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>408</v>
+      </c>
+      <c r="C407" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>408</v>
+      </c>
+      <c r="C408" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>408</v>
+      </c>
+      <c r="C409" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>408</v>
+      </c>
+      <c r="C410" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>408</v>
+      </c>
+      <c r="C411" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>408</v>
+      </c>
+      <c r="C412" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>408</v>
+      </c>
+      <c r="C413" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>408</v>
+      </c>
+      <c r="C414" s="3" t="s">
+        <v>382</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:C261">
-    <sortCondition ref="C2:C261"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C262:C306">
+    <sortCondition ref="C262:C306"/>
   </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/CombinedDataset.xlsx
+++ b/CombinedDataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stew\Documents\GitHub\HDS5106\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEA2045-3E34-479C-8E37-9B718605637C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D341165-74CE-4D00-A43D-971FA62A95F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{49767931-91A8-468D-A7BA-3084B4A3CD8D}"/>
   </bookViews>
@@ -10923,6 +10923,9 @@
       <c r="G307">
         <v>38.266494445773503</v>
       </c>
+      <c r="H307">
+        <v>5.9203734459350299</v>
+      </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
@@ -10946,6 +10949,9 @@
       <c r="G308">
         <v>11.165231619205301</v>
       </c>
+      <c r="H308">
+        <v>1.72647339300497</v>
+      </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
@@ -10969,6 +10975,9 @@
       <c r="G309">
         <v>14.295012009825101</v>
       </c>
+      <c r="H309">
+        <v>2.2105908956337399</v>
+      </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
@@ -10992,6 +11001,9 @@
       <c r="G310">
         <v>12.5120810659635</v>
       </c>
+      <c r="H310">
+        <v>1.9344294796835699</v>
+      </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
@@ -11015,6 +11027,9 @@
       <c r="G311">
         <v>9.0629283143448998</v>
       </c>
+      <c r="H311">
+        <v>1.4009783158985001</v>
+      </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
@@ -11038,6 +11053,9 @@
       <c r="G312">
         <v>11.968454294484401</v>
       </c>
+      <c r="H312">
+        <v>1.8495620927258201</v>
+      </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
@@ -11061,6 +11079,9 @@
       <c r="G313">
         <v>9.9854320393351799</v>
       </c>
+      <c r="H313">
+        <v>1.54207307722992</v>
+      </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
@@ -11084,6 +11105,9 @@
       <c r="G314">
         <v>20.769787987271499</v>
       </c>
+      <c r="H314">
+        <v>3.2102015528720602</v>
+      </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
@@ -11107,6 +11131,9 @@
       <c r="G315">
         <v>10.1630344692898</v>
       </c>
+      <c r="H315">
+        <v>1.5762463049904001</v>
+      </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
@@ -11130,6 +11157,9 @@
       <c r="G316">
         <v>11.3712991934465</v>
       </c>
+      <c r="H316">
+        <v>1.7565153568890599</v>
+      </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
@@ -11153,6 +11183,9 @@
       <c r="G317">
         <v>12.239909059457601</v>
       </c>
+      <c r="H317">
+        <v>1.89252639043288</v>
+      </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
@@ -11176,6 +11209,9 @@
       <c r="G318">
         <v>10.7160068985874</v>
       </c>
+      <c r="H318">
+        <v>1.6574641166631501</v>
+      </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
@@ -11199,6 +11235,9 @@
       <c r="G319">
         <v>11.953494950759101</v>
       </c>
+      <c r="H319">
+        <v>1.84836776054302</v>
+      </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
@@ -11222,8 +11261,11 @@
       <c r="G320">
         <v>15.052172606067501</v>
       </c>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H320">
+        <v>2.3309075425628301</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>408</v>
       </c>
@@ -11245,8 +11287,11 @@
       <c r="G321">
         <v>10.0688548423529</v>
       </c>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H321">
+        <v>1.5565857505882399</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>408</v>
       </c>
@@ -11268,8 +11313,11 @@
       <c r="G322">
         <v>9.9945586173897407</v>
       </c>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H322">
+        <v>1.5457825067195801</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>408</v>
       </c>
@@ -11291,8 +11339,11 @@
       <c r="G323">
         <v>10.1398278931073</v>
       </c>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H323">
+        <v>1.5682296746037601</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>408</v>
       </c>
@@ -11314,8 +11365,11 @@
       <c r="G324">
         <v>12.5564575809496</v>
       </c>
-    </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H324">
+        <v>1.9418642456900701</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>408</v>
       </c>
@@ -11337,8 +11391,11 @@
       <c r="G325">
         <v>21.148687006632599</v>
       </c>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H325">
+        <v>3.2700694356642002</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>408</v>
       </c>
@@ -11360,8 +11417,11 @@
       <c r="G326">
         <v>14.676458144954999</v>
       </c>
-    </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H326">
+        <v>2.2685030807663602</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>408</v>
       </c>
@@ -11383,8 +11443,11 @@
       <c r="G327">
         <v>9.8560123758104492</v>
       </c>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H327">
+        <v>1.52487709317218</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>408</v>
       </c>
@@ -11406,8 +11469,11 @@
       <c r="G328">
         <v>8.9986511885587603</v>
       </c>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H328">
+        <v>1.3953225804878</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>408</v>
       </c>
@@ -11429,8 +11495,11 @@
       <c r="G329">
         <v>11.664695420618999</v>
       </c>
-    </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H329">
+        <v>1.80380863148519</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>408</v>
       </c>
@@ -11452,8 +11521,11 @@
       <c r="G330">
         <v>7.3473230366459603</v>
       </c>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H330">
+        <v>1.14082329021739</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>408</v>
       </c>
@@ -11475,8 +11547,11 @@
       <c r="G331">
         <v>17.665422376851101</v>
       </c>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H331">
+        <v>2.7240402238243702</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>408</v>
       </c>
@@ -11498,8 +11573,11 @@
       <c r="G332">
         <v>16.140258351595701</v>
       </c>
-    </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H332">
+        <v>2.4930078027973099</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>408</v>
       </c>
@@ -11521,8 +11599,11 @@
       <c r="G333">
         <v>29.9727877249139</v>
       </c>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H333">
+        <v>4.6285614684271001</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>408</v>
       </c>
@@ -11544,8 +11625,11 @@
       <c r="G334">
         <v>19.721117173421899</v>
       </c>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H334">
+        <v>3.0491263900332202</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>408</v>
       </c>
@@ -11567,8 +11651,11 @@
       <c r="G335">
         <v>12.305829593693</v>
       </c>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H335">
+        <v>1.9159293118848</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>408</v>
       </c>
@@ -11590,8 +11677,11 @@
       <c r="G336">
         <v>14.1069427700573</v>
       </c>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H336">
+        <v>2.1813425300859599</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>408</v>
       </c>
@@ -11613,8 +11703,11 @@
       <c r="G337">
         <v>12.1761108596668</v>
       </c>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H337">
+        <v>1.88356527071465</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>408</v>
       </c>
@@ -11636,8 +11729,11 @@
       <c r="G338">
         <v>8.58168427024731</v>
       </c>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H338">
+        <v>1.3287858872947</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>408</v>
       </c>
@@ -11659,8 +11755,11 @@
       <c r="G339">
         <v>13.517480931010301</v>
       </c>
-    </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H339">
+        <v>2.0908538536139201</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>408</v>
       </c>
@@ -11682,8 +11781,11 @@
       <c r="G340">
         <v>9.7727534475370597</v>
       </c>
-    </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H340">
+        <v>1.5112285902439</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>408</v>
       </c>
@@ -11705,8 +11807,11 @@
       <c r="G341">
         <v>9.8453608549217897</v>
       </c>
-    </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H341">
+        <v>1.52149432878672</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>408</v>
       </c>
@@ -11728,8 +11833,11 @@
       <c r="G342">
         <v>15.5704559750261</v>
       </c>
-    </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H342">
+        <v>2.4054002819914699</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>408</v>
       </c>
@@ -11751,8 +11859,11 @@
       <c r="G343">
         <v>13.9618597481411</v>
       </c>
-    </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H343">
+        <v>2.15753147494982</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>408</v>
       </c>
@@ -11774,8 +11885,11 @@
       <c r="G344">
         <v>16.550978412844501</v>
       </c>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H344">
+        <v>2.5586178120115202</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>408</v>
       </c>
@@ -11797,8 +11911,11 @@
       <c r="G345">
         <v>13.4094363924431</v>
       </c>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H345">
+        <v>2.0738236955417202</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>408</v>
       </c>
@@ -11820,8 +11937,11 @@
       <c r="G346">
         <v>8.7860967763331903</v>
       </c>
-    </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H346">
+        <v>1.35846886109887</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>408</v>
       </c>
@@ -11843,8 +11963,11 @@
       <c r="G347">
         <v>19.5022491517195</v>
       </c>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H347">
+        <v>3.0159286099123399</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>408</v>
       </c>
@@ -11866,8 +11989,11 @@
       <c r="G348">
         <v>10.920367719270599</v>
       </c>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H348">
+        <v>1.6900201765709</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>408</v>
       </c>
@@ -11889,8 +12015,11 @@
       <c r="G349">
         <v>15.1752295509335</v>
       </c>
-    </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H349">
+        <v>2.3469277415656702</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>408</v>
       </c>
@@ -11912,8 +12041,11 @@
       <c r="G350">
         <v>8.5506206869579895</v>
       </c>
-    </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H350">
+        <v>1.3222616921950701</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>408</v>
       </c>
@@ -11935,8 +12067,11 @@
       <c r="G351">
         <v>17.1372432468964</v>
       </c>
-    </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H351">
+        <v>2.6482345121363702</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>408</v>
       </c>
@@ -11958,8 +12093,11 @@
       <c r="G352">
         <v>8.4787968111784693</v>
       </c>
-    </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H352">
+        <v>1.3110620371137101</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>408</v>
       </c>
@@ -11981,8 +12119,11 @@
       <c r="G353">
         <v>30.861905034419699</v>
       </c>
-    </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H353">
+        <v>4.7663021018512</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>408</v>
       </c>
@@ -12004,8 +12145,11 @@
       <c r="G354">
         <v>22.791713072423999</v>
       </c>
-    </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H354">
+        <v>3.52236129098238</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>408</v>
       </c>
@@ -12027,8 +12171,11 @@
       <c r="G355">
         <v>12.8496825785406</v>
       </c>
-    </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H355">
+        <v>1.9846520286818199</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>408</v>
       </c>
@@ -12050,8 +12197,11 @@
       <c r="G356">
         <v>14.7352550525727</v>
       </c>
-    </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H356">
+        <v>2.2756398366890398</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>408</v>
       </c>
@@ -12073,8 +12223,11 @@
       <c r="G357">
         <v>12.4724504111893</v>
       </c>
-    </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H357">
+        <v>1.9292693393792</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>408</v>
       </c>
@@ -12096,8 +12249,11 @@
       <c r="G358">
         <v>7.8016945295328801</v>
       </c>
-    </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H358">
+        <v>1.2061920626689</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>408</v>
       </c>
@@ -12119,8 +12275,11 @@
       <c r="G359">
         <v>11.000347897123699</v>
       </c>
-    </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H359">
+        <v>1.7008462172860599</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>408</v>
       </c>
@@ -12142,8 +12301,11 @@
       <c r="G360">
         <v>16.124103882912699</v>
       </c>
-    </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H360">
+        <v>2.4906103138596598</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>408</v>
       </c>
@@ -12165,8 +12327,11 @@
       <c r="G361">
         <v>15.2191469845098</v>
       </c>
-    </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H361">
+        <v>2.3515794297361099</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>408</v>
       </c>
@@ -12188,8 +12353,11 @@
       <c r="G362">
         <v>10.5206593280493</v>
       </c>
-    </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H362">
+        <v>1.62534359441341</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>408</v>
       </c>
@@ -12211,8 +12379,11 @@
       <c r="G363">
         <v>13.2267930363974</v>
       </c>
-    </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H363">
+        <v>2.0422348792217702</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>408</v>
       </c>
@@ -12234,8 +12405,11 @@
       <c r="G364">
         <v>13.27065632077</v>
       </c>
-    </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H364">
+        <v>2.0520760696495501</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>408</v>
       </c>
@@ -12257,8 +12431,11 @@
       <c r="G365">
         <v>14.0918965325471</v>
       </c>
-    </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H365">
+        <v>2.1802289410323201</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>408</v>
       </c>
@@ -12280,8 +12457,11 @@
       <c r="G366">
         <v>16.308096147190401</v>
       </c>
-    </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H366">
+        <v>2.5224403177134</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>408</v>
       </c>
@@ -12303,8 +12483,11 @@
       <c r="G367">
         <v>15.840476366031799</v>
       </c>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H367">
+        <v>2.44888174799283</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>408</v>
       </c>
@@ -12326,8 +12509,11 @@
       <c r="G368">
         <v>13.5442370535248</v>
       </c>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H368">
+        <v>2.0939791243644401</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>408</v>
       </c>
@@ -12349,8 +12535,11 @@
       <c r="G369">
         <v>23.7853116743666</v>
       </c>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H369">
+        <v>3.6764992492548401</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>408</v>
       </c>
@@ -12372,8 +12561,11 @@
       <c r="G370">
         <v>20.400631792559899</v>
       </c>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H370">
+        <v>3.1548186544766699</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>408</v>
       </c>
@@ -12395,8 +12587,11 @@
       <c r="G371">
         <v>21.3489512157518</v>
       </c>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H371">
+        <v>3.3022225379474901</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>408</v>
       </c>
@@ -12418,8 +12613,11 @@
       <c r="G372">
         <v>7.9314889300776903</v>
       </c>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H372">
+        <v>1.2263496303252801</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>408</v>
       </c>
@@ -12441,8 +12639,11 @@
       <c r="G373">
         <v>34.777064173126597</v>
       </c>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H373">
+        <v>5.3769097338501304</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>408</v>
       </c>
@@ -12464,8 +12665,11 @@
       <c r="G374">
         <v>21.7853134</v>
       </c>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H374">
+        <v>3.3702505173333299</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>408</v>
       </c>
@@ -12487,8 +12691,11 @@
       <c r="G375">
         <v>9.5751104367804007</v>
       </c>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H375">
+        <v>1.4802884306861801</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>408</v>
       </c>
@@ -12510,8 +12717,11 @@
       <c r="G376">
         <v>9.6197571844405605</v>
       </c>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H376">
+        <v>1.48634277528721</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>408</v>
       </c>
@@ -12533,8 +12743,11 @@
       <c r="G377">
         <v>9.0768435427109608</v>
       </c>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H377">
+        <v>1.4023904855098499</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>408</v>
       </c>
@@ -12556,8 +12769,11 @@
       <c r="G378">
         <v>17.5171452912872</v>
       </c>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H378">
+        <v>2.70625507790571</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>408</v>
       </c>
@@ -12579,8 +12795,11 @@
       <c r="G379">
         <v>18.0703906837166</v>
       </c>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H379">
+        <v>2.7931730353958599</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>408</v>
       </c>
@@ -12602,8 +12821,11 @@
       <c r="G380">
         <v>13.608277515331601</v>
       </c>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H380">
+        <v>2.1034446457060301</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>408</v>
       </c>
@@ -12625,8 +12847,11 @@
       <c r="G381">
         <v>10.2785545809253</v>
       </c>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H381">
+        <v>1.5891542482087799</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>408</v>
       </c>
@@ -12648,8 +12873,11 @@
       <c r="G382">
         <v>7.2618231352039402</v>
       </c>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H382">
+        <v>1.12274337896702</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>408</v>
       </c>
@@ -12671,8 +12899,11 @@
       <c r="G383">
         <v>12.570125503236399</v>
       </c>
-    </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H383">
+        <v>1.9430058090150499</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>408</v>
       </c>
@@ -12694,8 +12925,11 @@
       <c r="G384">
         <v>13.975932167985301</v>
       </c>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H384">
+        <v>2.1598034947725302</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>408</v>
       </c>
@@ -12717,8 +12951,11 @@
       <c r="G385">
         <v>10.8019336572823</v>
       </c>
-    </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H385">
+        <v>1.6705166606606601</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>408</v>
       </c>
@@ -12740,8 +12977,11 @@
       <c r="G386">
         <v>14.802770087695</v>
       </c>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H386">
+        <v>2.2894082189823601</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>408</v>
       </c>
@@ -12763,8 +13003,11 @@
       <c r="G387">
         <v>10.2408159100438</v>
       </c>
-    </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H387">
+        <v>1.5829804961883001</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>408</v>
       </c>
@@ -12786,8 +13029,11 @@
       <c r="G388">
         <v>29.354384973302999</v>
       </c>
-    </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H388">
+        <v>4.5361547335984103</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>408</v>
       </c>
@@ -12809,8 +13055,11 @@
       <c r="G389">
         <v>14.8275103181404</v>
       </c>
-    </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H389">
+        <v>2.2910393992707401</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>408</v>
       </c>
@@ -12832,8 +13081,11 @@
       <c r="G390">
         <v>17.644432011890601</v>
       </c>
-    </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H390">
+        <v>2.7279322347651598</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>408</v>
       </c>
@@ -12855,8 +13107,11 @@
       <c r="G391">
         <v>16.699223391761802</v>
       </c>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H391">
+        <v>2.5806732642640502</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>408</v>
       </c>
@@ -12878,8 +13133,11 @@
       <c r="G392">
         <v>13.162284237941099</v>
       </c>
-    </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H392">
+        <v>2.0368175265255299</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>408</v>
       </c>
@@ -12901,8 +13159,11 @@
       <c r="G393">
         <v>10.1245458337767</v>
       </c>
-    </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H393">
+        <v>1.5660099010322399</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>408</v>
       </c>
@@ -12924,8 +13185,11 @@
       <c r="G394">
         <v>10.6388563233971</v>
       </c>
-    </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H394">
+        <v>1.6469439859392601</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>408</v>
       </c>
@@ -12947,8 +13211,11 @@
       <c r="G395">
         <v>12.3954241125591</v>
       </c>
-    </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H395">
+        <v>1.91820572083812</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>408</v>
       </c>
@@ -12970,8 +13237,11 @@
       <c r="G396">
         <v>9.2398366563839307</v>
       </c>
-    </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H396">
+        <v>1.4293565555987</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>408</v>
       </c>
@@ -12993,8 +13263,11 @@
       <c r="G397">
         <v>13.344175087019501</v>
       </c>
-    </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H397">
+        <v>2.07378855922006</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>408</v>
       </c>
@@ -13016,8 +13289,11 @@
       <c r="G398">
         <v>7.7824606020511702</v>
       </c>
-    </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H398">
+        <v>1.20469952879522</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>408</v>
       </c>
@@ -13039,8 +13315,11 @@
       <c r="G399">
         <v>23.769741730998302</v>
       </c>
-    </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H399">
+        <v>3.6727411037401101</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>408</v>
       </c>
@@ -13062,8 +13341,11 @@
       <c r="G400">
         <v>32.518903985090702</v>
       </c>
-    </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H400">
+        <v>5.0168235985244403</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>408</v>
       </c>
@@ -13085,8 +13367,11 @@
       <c r="G401">
         <v>11.2587839223396</v>
       </c>
-    </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H401">
+        <v>1.7406982386963801</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>408</v>
       </c>
@@ -13108,8 +13393,11 @@
       <c r="G402">
         <v>8.4534210194563908</v>
       </c>
-    </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H402">
+        <v>1.3071014028157999</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>408</v>
       </c>
@@ -13131,8 +13419,11 @@
       <c r="G403">
         <v>11.0186237702751</v>
       </c>
-    </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H403">
+        <v>1.7048237169165401</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>408</v>
       </c>
@@ -13154,8 +13445,11 @@
       <c r="G404">
         <v>13.852961343518199</v>
       </c>
-    </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H404">
+        <v>2.13029417546722</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>408</v>
       </c>
@@ -13177,8 +13471,11 @@
       <c r="G405">
         <v>10.6802511111824</v>
       </c>
-    </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H405">
+        <v>1.65155694017204</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>408</v>
       </c>
@@ -13200,8 +13497,11 @@
       <c r="G406">
         <v>15.0368685346434</v>
       </c>
-    </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H406">
+        <v>2.3258582886308501</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>408</v>
       </c>
@@ -13223,8 +13523,11 @@
       <c r="G407">
         <v>10.846516516320801</v>
       </c>
-    </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H407">
+        <v>1.6813972812170199</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>408</v>
       </c>
@@ -13246,8 +13549,11 @@
       <c r="G408">
         <v>9.9158842378815102</v>
       </c>
-    </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H408">
+        <v>1.5311704746858199</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>408</v>
       </c>
@@ -13269,8 +13575,11 @@
       <c r="G409">
         <v>12.165559027827101</v>
       </c>
-    </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H409">
+        <v>1.8802744731408301</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>408</v>
       </c>
@@ -13292,8 +13601,11 @@
       <c r="G410">
         <v>12.4329292619444</v>
       </c>
-    </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H410">
+        <v>1.92155478157979</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>408</v>
       </c>
@@ -13315,8 +13627,11 @@
       <c r="G411">
         <v>7.7914211641699804</v>
       </c>
-    </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H411">
+        <v>1.2054060055028999</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>408</v>
       </c>
@@ -13338,8 +13653,11 @@
       <c r="G412">
         <v>16.416526483712701</v>
       </c>
-    </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H412">
+        <v>2.5386274762446699</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>408</v>
       </c>
@@ -13361,8 +13679,11 @@
       <c r="G413">
         <v>12.7957541598741</v>
       </c>
-    </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H413">
+        <v>1.9777221111776999</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>408</v>
       </c>
@@ -13383,6 +13704,9 @@
       </c>
       <c r="G414">
         <v>13.149091058199</v>
+      </c>
+      <c r="H414">
+        <v>2.03185892039519</v>
       </c>
     </row>
   </sheetData>

--- a/CombinedDataset.xlsx
+++ b/CombinedDataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stew\Documents\GitHub\HDS5106\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D341165-74CE-4D00-A43D-971FA62A95F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D07017-9E5C-411B-85BD-48E264632646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{49767931-91A8-468D-A7BA-3084B4A3CD8D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="838">
   <si>
     <t>Country</t>
   </si>
@@ -2550,6 +2550,9 @@
   </si>
   <si>
     <t>Asunafo North Municipal</t>
+  </si>
+  <si>
+    <t>Travel Time</t>
   </si>
 </sst>
 </file>
@@ -2937,7 +2940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE93494-9460-4C4F-AAB4-84EDA70370DB}">
-  <dimension ref="A1:H414"/>
+  <dimension ref="A1:I414"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2948,7 +2951,7 @@
     <col min="8" max="8" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2970,8 +2973,11 @@
       <c r="H1" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2996,8 +3002,11 @@
       <c r="H2">
         <v>6.1852835246893898</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <v>96.761533852606306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3022,8 +3031,11 @@
       <c r="H3">
         <v>3.2897105240044699</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <v>78.184088806660498</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -3048,8 +3060,11 @@
       <c r="H4">
         <v>3.0475143326446301</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <v>100.48872858431</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3074,8 +3089,11 @@
       <c r="H5">
         <v>3.04084080876068</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <v>74.786931818181799</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3100,8 +3118,11 @@
       <c r="H6">
         <v>1.6288042863573</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <v>82.241658240647098</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -3126,8 +3147,11 @@
       <c r="H7">
         <v>1.4146286888019199</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7">
+        <v>78.951724137930995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3152,8 +3176,11 @@
       <c r="H8">
         <v>2.3076367633223098</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8">
+        <v>90.776946107784397</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -3178,8 +3205,11 @@
       <c r="H9">
         <v>1.3849098447755199</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9">
+        <v>91.675213675213698</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -3204,8 +3234,11 @@
       <c r="H10">
         <v>1.0615774784482801</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10">
+        <v>51.685430463576203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -3230,8 +3263,11 @@
       <c r="H11">
         <v>1.3715497329161901</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11">
+        <v>97.483762597984295</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -3256,8 +3292,11 @@
       <c r="H12">
         <v>3.9739334783313098</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12">
+        <v>57.283783783783797</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -3282,8 +3321,11 @@
       <c r="H13">
         <v>1.37516294946156</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13">
+        <v>41.022813688212899</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -3308,8 +3350,11 @@
       <c r="H14">
         <v>3.1637357565660502</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14">
+        <v>73.857142857142904</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -3334,8 +3379,11 @@
       <c r="H15">
         <v>1.8478468229148499</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15">
+        <v>76.183850931677</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -3360,8 +3408,11 @@
       <c r="H16">
         <v>1.91059413467049</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16">
+        <v>87.421585160202397</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -3386,8 +3437,11 @@
       <c r="H17">
         <v>1.4273190971309</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17">
+        <v>83.225774225774202</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -3412,8 +3466,11 @@
       <c r="H18">
         <v>2.0045598624319401</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18">
+        <v>67.246808510638303</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -3438,8 +3495,11 @@
       <c r="H19">
         <v>1.97499135785441</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19">
+        <v>64.020026702269703</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -3464,8 +3524,11 @@
       <c r="H20">
         <v>1.0820797686646499</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20">
+        <v>58.511299435028199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -3490,8 +3553,11 @@
       <c r="H21">
         <v>1.0912417568389099</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21">
+        <v>135.657358490566</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -3516,8 +3582,11 @@
       <c r="H22">
         <v>1.9884858884177601</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22">
+        <v>67.942477876106196</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -3542,8 +3611,11 @@
       <c r="H23">
         <v>11.073452273331901</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23">
+        <v>27.807692307692299</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -3568,8 +3640,11 @@
       <c r="H24">
         <v>11.202292</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -3594,8 +3669,11 @@
       <c r="H25">
         <v>1.5203474629812399</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25">
+        <v>41.989864864864899</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -3620,8 +3698,11 @@
       <c r="H26">
         <v>2.6905025905737099</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26">
+        <v>107.596032461677</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -3646,8 +3727,11 @@
       <c r="H27">
         <v>1.05364772116935</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27">
+        <v>71.677419354838705</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -3672,8 +3756,11 @@
       <c r="H28">
         <v>1.04757643582737</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28">
+        <v>57.6340326340326</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -3698,8 +3785,11 @@
       <c r="H29">
         <v>1.6345592250146099</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29">
+        <v>59.609177215189902</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -3724,8 +3814,11 @@
       <c r="H30">
         <v>1.5217176304229401</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30">
+        <v>78.753731343283604</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -3750,8 +3843,11 @@
       <c r="H31">
         <v>1.1428528932234401</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31">
+        <v>48.602409638554199</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -3776,8 +3872,11 @@
       <c r="H32">
         <v>1.01312847030511</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32">
+        <v>46.136082474226797</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -3802,8 +3901,11 @@
       <c r="H33">
         <v>1.2763670935633</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33">
+        <v>90.038583175205602</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -3828,8 +3930,11 @@
       <c r="H34">
         <v>0.67459267629629605</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34">
+        <v>73.926108374384199</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -3854,8 +3959,11 @@
       <c r="H35">
         <v>11.202292</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35">
+        <v>7.1153846153846096</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -3880,8 +3988,11 @@
       <c r="H36">
         <v>0.444283293938109</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36">
+        <v>22.684931506849299</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -3906,8 +4017,11 @@
       <c r="H37">
         <v>10.8014701161043</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37">
+        <v>16.544303797468402</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -3932,8 +4046,11 @@
       <c r="H38">
         <v>1.2388094203584401</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38">
+        <v>81.002560819462204</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -3958,8 +4075,11 @@
       <c r="H39">
         <v>1.0078308264856299</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39">
+        <v>56.775280898876403</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -3984,8 +4104,11 @@
       <c r="H40">
         <v>1.75804320226321</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40">
+        <v>48.664705882352898</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -4010,8 +4133,11 @@
       <c r="H41">
         <v>0.99586757501015</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41">
+        <v>77.735465116279101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -4036,8 +4162,11 @@
       <c r="H42">
         <v>1.15928687214342</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42">
+        <v>135.96872207327999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -4062,8 +4191,11 @@
       <c r="H43">
         <v>10.628206200068099</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43">
+        <v>18.3888888888889</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -4088,8 +4220,11 @@
       <c r="H44">
         <v>7.7848445123577896</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44">
+        <v>17.2777777777778</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -4114,8 +4249,11 @@
       <c r="H45">
         <v>1.98443201186673</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I45">
+        <v>148.814974802016</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -4140,8 +4278,11 @@
       <c r="H46">
         <v>1.51729141783675</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46">
+        <v>92.099220779220801</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -4166,8 +4307,11 @@
       <c r="H47">
         <v>0.66307300000000002</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47">
+        <v>50.176895306859201</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -4192,8 +4336,11 @@
       <c r="H48">
         <v>1.6574256444731701</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48">
+        <v>78.378497790868906</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -4218,8 +4365,11 @@
       <c r="H49">
         <v>2.4118277511330901</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I49">
+        <v>45.174442190669403</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -4244,8 +4394,11 @@
       <c r="H50">
         <v>9.8371822201684598</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I50">
+        <v>23.272727272727298</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -4270,8 +4423,11 @@
       <c r="H51">
         <v>1.90494865583634</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I51">
+        <v>164.42820324005899</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -4296,8 +4452,11 @@
       <c r="H52">
         <v>2.1410593852262698</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52">
+        <v>100.19669117647101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -4322,8 +4481,11 @@
       <c r="H53">
         <v>2.1418518365414001</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I53">
+        <v>72.884453781512605</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -4348,8 +4510,11 @@
       <c r="H54">
         <v>2.4076526171964301</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I54">
+        <v>102.08805970149299</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -4374,8 +4539,11 @@
       <c r="H55">
         <v>2.71524607064622</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I55">
+        <v>100.570126227209</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -4400,8 +4568,11 @@
       <c r="H56">
         <v>2.7188119999999998</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I56">
+        <v>89.839285714285694</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -4426,8 +4597,11 @@
       <c r="H57">
         <v>1.6843422233068199</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I57">
+        <v>50.222678718159401</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -4452,8 +4626,11 @@
       <c r="H58">
         <v>1.737616</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I58">
+        <v>56.187147688838799</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -4478,8 +4655,11 @@
       <c r="H59">
         <v>1.06809740401853</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I59">
+        <v>72.787269681742004</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -4504,8 +4684,11 @@
       <c r="H60">
         <v>1.2845902429809399</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I60">
+        <v>99.669887278582905</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -4530,8 +4713,11 @@
       <c r="H61">
         <v>1.90147808086785</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I61">
+        <v>109.814200092208</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -4556,8 +4742,11 @@
       <c r="H62">
         <v>1.47389548791852</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I62">
+        <v>102.065974796145</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -4582,8 +4771,11 @@
       <c r="H63">
         <v>2.06664225513906</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I63">
+        <v>119.844344183049</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -4608,8 +4800,11 @@
       <c r="H64">
         <v>1.47005101550748</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I64">
+        <v>217.45451394905601</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -4634,8 +4829,11 @@
       <c r="H65">
         <v>1.29597428129541</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I65">
+        <v>125.79698828778599</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -4660,8 +4858,11 @@
       <c r="H66">
         <v>2.1242945405355802</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I66">
+        <v>121.63802559414999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -4686,8 +4887,11 @@
       <c r="H67">
         <v>1.91370766956711</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I67">
+        <v>95.331792975970401</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>4</v>
       </c>
@@ -4712,8 +4916,11 @@
       <c r="H68">
         <v>3.6332005813953501</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I68">
+        <v>143.591165896251</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -4738,8 +4945,11 @@
       <c r="H69">
         <v>3.58515128589368</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I69">
+        <v>157.36260162601599</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>4</v>
       </c>
@@ -4764,8 +4974,11 @@
       <c r="H70">
         <v>1.5975520300192401</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I70">
+        <v>294.55088666152699</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -4790,8 +5003,11 @@
       <c r="H71">
         <v>1.94569044640884</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I71">
+        <v>219.35929387331299</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -4816,8 +5032,11 @@
       <c r="H72">
         <v>1.03670774634559</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I72">
+        <v>53.613577023498699</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>4</v>
       </c>
@@ -4842,8 +5061,11 @@
       <c r="H73">
         <v>1.0342810263255</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I73">
+        <v>62.408207343412499</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>4</v>
       </c>
@@ -4868,8 +5090,11 @@
       <c r="H74">
         <v>1.74910621399947</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I74">
+        <v>30.031460674157302</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>4</v>
       </c>
@@ -4894,8 +5119,11 @@
       <c r="H75">
         <v>1.7202070081138301</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I75">
+        <v>42.973684210526301</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>4</v>
       </c>
@@ -4920,8 +5148,11 @@
       <c r="H76">
         <v>1.9279587370179201</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I76">
+        <v>43.380614657210401</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>4</v>
       </c>
@@ -4946,8 +5177,11 @@
       <c r="H77">
         <v>3.4789326103390099</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I77">
+        <v>34.328382838283801</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>4</v>
       </c>
@@ -4972,8 +5206,11 @@
       <c r="H78">
         <v>3.0592053917035602</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I78">
+        <v>64.455737704917993</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>4</v>
       </c>
@@ -4998,8 +5235,11 @@
       <c r="H79">
         <v>2.2031673993957699</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I79">
+        <v>85.300300300300293</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>4</v>
       </c>
@@ -5024,8 +5264,11 @@
       <c r="H80">
         <v>2.2084342842220099</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I80">
+        <v>80.567567567567593</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -5050,8 +5293,11 @@
       <c r="H81">
         <v>3.3861046475205101</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I81">
+        <v>128.23410852713201</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -5076,8 +5322,11 @@
       <c r="H82">
         <v>0.74686822312176204</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I82">
+        <v>29.668989547038301</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -5102,8 +5351,11 @@
       <c r="H83">
         <v>0.76633812422784497</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I83">
+        <v>36.9527559055118</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -5128,8 +5380,11 @@
       <c r="H84">
         <v>1.4644733502870499</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I84">
+        <v>21.876811594202898</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>4</v>
       </c>
@@ -5154,8 +5409,11 @@
       <c r="H85">
         <v>1.3151936860590601</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I85">
+        <v>28.28125</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>4</v>
       </c>
@@ -5180,8 +5438,11 @@
       <c r="H86">
         <v>1.16202393609023</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I86">
+        <v>41.036809815950903</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>4</v>
       </c>
@@ -5206,8 +5467,11 @@
       <c r="H87">
         <v>1.28508928533333</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I87">
+        <v>46.297872340425499</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>4</v>
       </c>
@@ -5232,8 +5496,11 @@
       <c r="H88">
         <v>0.966976635146226</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I88">
+        <v>39.140157480314997</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -5258,8 +5525,11 @@
       <c r="H89">
         <v>1.2995404387726599</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I89">
+        <v>33.957070707070699</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>4</v>
       </c>
@@ -5284,8 +5554,11 @@
       <c r="H90">
         <v>1.2456205217501599</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I90">
+        <v>46.057943925233602</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -5310,8 +5583,11 @@
       <c r="H91">
         <v>1.1561500332682</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I91">
+        <v>38.535211267605597</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>4</v>
       </c>
@@ -5336,8 +5612,11 @@
       <c r="H92">
         <v>1.00337320030669</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I92">
+        <v>99.674709562109001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>4</v>
       </c>
@@ -5362,8 +5641,11 @@
       <c r="H93">
         <v>1.0174810621721699</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I93">
+        <v>90.869436201780402</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>4</v>
       </c>
@@ -5388,8 +5670,11 @@
       <c r="H94">
         <v>4.3961296569230797</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I94">
+        <v>59.586846543001698</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -5414,8 +5699,11 @@
       <c r="H95">
         <v>2.18266519578947</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I95">
+        <v>63.465390279823303</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -5440,8 +5728,11 @@
       <c r="H96">
         <v>2.9499221295311702</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I96">
+        <v>47.423280423280403</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -5466,8 +5757,11 @@
       <c r="H97">
         <v>2.9577310675044299</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I97">
+        <v>53.745762711864401</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>4</v>
       </c>
@@ -5492,8 +5786,11 @@
       <c r="H98">
         <v>4.9629680677518699</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I98">
+        <v>79.214876033057806</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>4</v>
       </c>
@@ -5518,8 +5815,11 @@
       <c r="H99">
         <v>2.1372227745424301</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I99">
+        <v>43.8960674157303</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>4</v>
       </c>
@@ -5544,8 +5844,11 @@
       <c r="H100">
         <v>0.67831577904801499</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I100">
+        <v>50.973484848484901</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>4</v>
       </c>
@@ -5570,8 +5873,11 @@
       <c r="H101">
         <v>8.0021678410985793</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I101">
+        <v>57.5048678720445</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>4</v>
       </c>
@@ -5596,8 +5902,11 @@
       <c r="H102">
         <v>3.3405769974293098</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I102">
+        <v>81.644578313253007</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -5622,8 +5931,11 @@
       <c r="H103">
         <v>0.57951125108958002</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I103">
+        <v>107.447777777778</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>4</v>
       </c>
@@ -5648,8 +5960,11 @@
       <c r="H104">
         <v>2.7647917265243098</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I104">
+        <v>101.93128654970801</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>4</v>
       </c>
@@ -5674,8 +5989,11 @@
       <c r="H105">
         <v>2.8301330226982899</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I105">
+        <v>144.47971014492799</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>4</v>
       </c>
@@ -5700,8 +6018,11 @@
       <c r="H106">
         <v>2.1467399306094901</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I106">
+        <v>61.078902229845603</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>4</v>
       </c>
@@ -5726,8 +6047,11 @@
       <c r="H107">
         <v>3.3510719831932798</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I107">
+        <v>40.2222222222222</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>4</v>
       </c>
@@ -5752,8 +6076,11 @@
       <c r="H108">
         <v>2.75923458359402</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I108">
+        <v>69.601796407185603</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -5778,8 +6105,11 @@
       <c r="H109">
         <v>4.6481411076008801</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I109">
+        <v>74.170270270270294</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -5804,8 +6134,11 @@
       <c r="H110">
         <v>3.5272646471663598</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I110">
+        <v>55.058823529411796</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>4</v>
       </c>
@@ -5830,8 +6163,11 @@
       <c r="H111">
         <v>2.5208044695331</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I111">
+        <v>179.441742654509</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>4</v>
       </c>
@@ -5856,8 +6192,11 @@
       <c r="H112">
         <v>2.53015578415576</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I112">
+        <v>50.8441558441558</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>4</v>
       </c>
@@ -5882,8 +6221,11 @@
       <c r="H113">
         <v>3.5090370502248902</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I113">
+        <v>68.004219409282697</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>4</v>
       </c>
@@ -5908,8 +6250,11 @@
       <c r="H114">
         <v>2.4837856018306601</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I114">
+        <v>273.75453885257798</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>4</v>
       </c>
@@ -5934,8 +6279,11 @@
       <c r="H115">
         <v>4.9847224405129396</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I115">
+        <v>172.917647058824</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>4</v>
       </c>
@@ -5960,8 +6308,11 @@
       <c r="H116">
         <v>1.07274084654823</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I116">
+        <v>104.840816326531</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>4</v>
       </c>
@@ -5986,8 +6337,11 @@
       <c r="H117">
         <v>1.1355575578252699</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I117">
+        <v>121.55460385439</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>4</v>
       </c>
@@ -6012,8 +6366,11 @@
       <c r="H118">
         <v>1.21955722433659</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I118">
+        <v>60.383966244725698</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>4</v>
       </c>
@@ -6038,8 +6395,11 @@
       <c r="H119">
         <v>0.51578898478920099</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I119">
+        <v>58.479224376731302</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>4</v>
       </c>
@@ -6064,8 +6424,11 @@
       <c r="H120">
         <v>1.1342737746793099</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I120">
+        <v>39.911290322580598</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>4</v>
       </c>
@@ -6090,8 +6453,11 @@
       <c r="H121">
         <v>1.1197655034242699</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I121">
+        <v>17.640625</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>4</v>
       </c>
@@ -6116,8 +6482,11 @@
       <c r="H122">
         <v>0.55362046630144002</v>
       </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I122">
+        <v>39.278846153846203</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -6142,8 +6511,11 @@
       <c r="H123">
         <v>1.8297769450297801</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I123">
+        <v>48.456043956043999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -6168,8 +6540,11 @@
       <c r="H124">
         <v>2.1232814299264899</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I124">
+        <v>47.124105011933203</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>4</v>
       </c>
@@ -6194,8 +6569,11 @@
       <c r="H125">
         <v>4.1685429821200497</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I125">
+        <v>123.653162055336</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>4</v>
       </c>
@@ -6220,8 +6598,11 @@
       <c r="H126">
         <v>2.7929076927316601</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I126">
+        <v>61.397022332506197</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>4</v>
       </c>
@@ -6246,8 +6627,11 @@
       <c r="H127">
         <v>3.1235656132276199</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I127">
+        <v>81.203208556149704</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>4</v>
       </c>
@@ -6272,8 +6656,11 @@
       <c r="H128">
         <v>1.0431189176876301</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I128">
+        <v>49.8645276292335</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>4</v>
       </c>
@@ -6298,8 +6685,11 @@
       <c r="H129">
         <v>3.3638710000000001</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I129">
+        <v>10.647058823529401</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>4</v>
       </c>
@@ -6324,8 +6714,11 @@
       <c r="H130">
         <v>3.2299931413547598</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I130">
+        <v>14.382352941176499</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -6350,8 +6743,11 @@
       <c r="H131">
         <v>3.3638710000000001</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I131">
+        <v>9.2666666666666693</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -6376,8 +6772,11 @@
       <c r="H132">
         <v>3.3638710000000001</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I132">
+        <v>3.6666666666666701</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>4</v>
       </c>
@@ -6402,8 +6801,11 @@
       <c r="H133">
         <v>0.53020926815617797</v>
       </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I133">
+        <v>61.771513353115701</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>4</v>
       </c>
@@ -6428,8 +6830,11 @@
       <c r="H134">
         <v>0.50527782575574398</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I134">
+        <v>75.754617414248003</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>4</v>
       </c>
@@ -6454,8 +6859,11 @@
       <c r="H135">
         <v>0.436785050810654</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I135">
+        <v>33.709677419354797</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>4</v>
       </c>
@@ -6480,8 +6888,11 @@
       <c r="H136">
         <v>1.85691091215195</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I136">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>4</v>
       </c>
@@ -6506,8 +6917,11 @@
       <c r="H137">
         <v>3.3638710000000001</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -6532,8 +6946,11 @@
       <c r="H138">
         <v>3.3638710000000001</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I138">
+        <v>1.8333333333333299</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>4</v>
       </c>
@@ -6558,8 +6975,11 @@
       <c r="H139">
         <v>3.3638710000000001</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I139">
+        <v>9.8333333333333304</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>4</v>
       </c>
@@ -6584,8 +7004,11 @@
       <c r="H140">
         <v>2.7286242778922301</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I140">
+        <v>8.1190476190476204</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>4</v>
       </c>
@@ -6610,8 +7033,11 @@
       <c r="H141">
         <v>0.57960507519119997</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I141">
+        <v>33.644067796610202</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>4</v>
       </c>
@@ -6636,8 +7062,11 @@
       <c r="H142">
         <v>0.83005337783201705</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I142">
+        <v>23.887755102040799</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>4</v>
       </c>
@@ -6662,8 +7091,11 @@
       <c r="H143">
         <v>0.37875045414847203</v>
       </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I143">
+        <v>44.919463087248303</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>4</v>
       </c>
@@ -6688,8 +7120,11 @@
       <c r="H144">
         <v>0.63300246321311504</v>
       </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I144">
+        <v>53.526570048309203</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>4</v>
       </c>
@@ -6714,8 +7149,11 @@
       <c r="H145">
         <v>0.38441905585665798</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I145">
+        <v>38.141463414634103</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>4</v>
       </c>
@@ -6740,8 +7178,11 @@
       <c r="H146">
         <v>3.3638710000000001</v>
       </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I146">
+        <v>5.0769230769230802</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>4</v>
       </c>
@@ -6766,8 +7207,11 @@
       <c r="H147">
         <v>0.79996634504480901</v>
       </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I147">
+        <v>43.542857142857102</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>4</v>
       </c>
@@ -6792,8 +7236,11 @@
       <c r="H148">
         <v>1.37495953434066</v>
       </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I148">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>4</v>
       </c>
@@ -6818,8 +7265,11 @@
       <c r="H149">
         <v>3.1182349370209699</v>
       </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I149">
+        <v>17.928571428571399</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>4</v>
       </c>
@@ -6844,8 +7294,11 @@
       <c r="H150">
         <v>0.87042518622946297</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I150">
+        <v>17.5058823529412</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -6870,8 +7323,11 @@
       <c r="H151">
         <v>1.4314340709304301</v>
       </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I151">
+        <v>12.909090909090899</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>4</v>
       </c>
@@ -6896,8 +7352,11 @@
       <c r="H152">
         <v>0.13043437275736999</v>
       </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I152">
+        <v>65.318801089918296</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>4</v>
       </c>
@@ -6922,8 +7381,11 @@
       <c r="H153">
         <v>3.0765751647672701</v>
       </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I153">
+        <v>10.846153846153801</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>4</v>
       </c>
@@ -6948,8 +7410,11 @@
       <c r="H154">
         <v>0.14513149094877001</v>
       </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I154">
+        <v>87.508326029798397</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>4</v>
       </c>
@@ -6974,8 +7439,11 @@
       <c r="H155">
         <v>0.76793123950369702</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I155">
+        <v>15.192307692307701</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>4</v>
       </c>
@@ -7000,8 +7468,11 @@
       <c r="H156">
         <v>1.2850282773825501</v>
       </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I156">
+        <v>19.462962962963001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>4</v>
       </c>
@@ -7026,8 +7497,11 @@
       <c r="H157">
         <v>0.700379353726575</v>
       </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I157">
+        <v>37.942105263157899</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>4</v>
       </c>
@@ -7052,8 +7526,11 @@
       <c r="H158">
         <v>3.2968464234389501</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I158">
+        <v>130.38200125865299</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>4</v>
       </c>
@@ -7078,8 +7555,11 @@
       <c r="H159">
         <v>3.5576618464811198</v>
       </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I159">
+        <v>113.994336569579</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>4</v>
       </c>
@@ -7104,8 +7584,11 @@
       <c r="H160">
         <v>2.3266502171390901</v>
       </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I160">
+        <v>91.5605718585403</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>4</v>
       </c>
@@ -7130,8 +7613,11 @@
       <c r="H161">
         <v>0.73492716234211297</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I161">
+        <v>135.26160567995601</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>4</v>
       </c>
@@ -7156,8 +7642,11 @@
       <c r="H162">
         <v>2.81888510918367</v>
       </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I162">
+        <v>112.24602927436899</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>4</v>
       </c>
@@ -7182,8 +7671,11 @@
       <c r="H163">
         <v>2.4745425443037998</v>
       </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I163">
+        <v>93.142605633802802</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>4</v>
       </c>
@@ -7208,8 +7700,11 @@
       <c r="H164">
         <v>2.4513274029863301</v>
       </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I164">
+        <v>132.14061917195099</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>4</v>
       </c>
@@ -7234,8 +7729,11 @@
       <c r="H165">
         <v>2.8569221766739799</v>
       </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I165">
+        <v>100.003312825367</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>4</v>
       </c>
@@ -7260,8 +7758,11 @@
       <c r="H166">
         <v>0.98915432364729405</v>
       </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I166">
+        <v>114.254212806933</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>4</v>
       </c>
@@ -7286,8 +7787,11 @@
       <c r="H167">
         <v>0.94750232510224197</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I167">
+        <v>38.25</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>4</v>
       </c>
@@ -7312,8 +7816,11 @@
       <c r="H168">
         <v>2.4028212540834799</v>
       </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I168">
+        <v>98.075040783034297</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>4</v>
       </c>
@@ -7338,8 +7845,11 @@
       <c r="H169">
         <v>0.93706470127863895</v>
       </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I169">
+        <v>83.46875</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>4</v>
       </c>
@@ -7364,8 +7874,11 @@
       <c r="H170">
         <v>1.4911711137460799</v>
       </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I170">
+        <v>108.918272937548</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>4</v>
       </c>
@@ -7390,8 +7903,11 @@
       <c r="H171">
         <v>0.73407467014328898</v>
       </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I171">
+        <v>131.37937500000001</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>4</v>
       </c>
@@ -7416,8 +7932,11 @@
       <c r="H172">
         <v>2.0945385271064998</v>
       </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I172">
+        <v>109.554265815438</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>4</v>
       </c>
@@ -7442,8 +7961,11 @@
       <c r="H173">
         <v>1.4874372046179201</v>
       </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I173">
+        <v>85.625668449197903</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>4</v>
       </c>
@@ -7468,8 +7990,11 @@
       <c r="H174">
         <v>1.6073140684612599</v>
       </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I174">
+        <v>87.503267973856197</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>4</v>
       </c>
@@ -7494,8 +8019,11 @@
       <c r="H175">
         <v>0.814948149428812</v>
       </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I175">
+        <v>112.60576333537701</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>4</v>
       </c>
@@ -7520,8 +8048,11 @@
       <c r="H176">
         <v>2.1776262233322301</v>
       </c>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I176">
+        <v>82.759231905465299</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>4</v>
       </c>
@@ -7546,8 +8077,11 @@
       <c r="H177">
         <v>2.2530159234653202</v>
       </c>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I177">
+        <v>118.689873417722</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>4</v>
       </c>
@@ -7572,8 +8106,11 @@
       <c r="H178">
         <v>2.2546456644951101</v>
       </c>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I178">
+        <v>118.76265720735201</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>4</v>
       </c>
@@ -7598,8 +8135,11 @@
       <c r="H179">
         <v>2.1276821191749402</v>
       </c>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I179">
+        <v>81.068965517241395</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>4</v>
       </c>
@@ -7624,8 +8164,11 @@
       <c r="H180">
         <v>0.78047366120056805</v>
       </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I180">
+        <v>146.80335365853699</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>4</v>
       </c>
@@ -7650,8 +8193,11 @@
       <c r="H181">
         <v>0.47154653947256098</v>
       </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I181">
+        <v>45.981566820276498</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>4</v>
       </c>
@@ -7676,8 +8222,11 @@
       <c r="H182">
         <v>0.71030912875152497</v>
       </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I182">
+        <v>51.895061728395099</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>4</v>
       </c>
@@ -7702,8 +8251,11 @@
       <c r="H183">
         <v>0.89167517179614497</v>
       </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I183">
+        <v>256.52717224439698</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>4</v>
       </c>
@@ -7728,8 +8280,11 @@
       <c r="H184">
         <v>2.0824279661499498</v>
       </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I184">
+        <v>88.0651558073654</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>4</v>
       </c>
@@ -7754,8 +8309,11 @@
       <c r="H185">
         <v>1.8268793607618301</v>
       </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I185">
+        <v>107.692798541477</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>4</v>
       </c>
@@ -7780,8 +8338,11 @@
       <c r="H186">
         <v>0.82325080028801501</v>
       </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I186">
+        <v>101.29326186829999</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>4</v>
       </c>
@@ -7806,8 +8367,11 @@
       <c r="H187">
         <v>0.92608809484168997</v>
       </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I187">
+        <v>92.346034696406406</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>4</v>
       </c>
@@ -7832,8 +8396,11 @@
       <c r="H188">
         <v>1.1231714780109201</v>
       </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I188">
+        <v>170.34378852212001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>4</v>
       </c>
@@ -7858,8 +8425,11 @@
       <c r="H189">
         <v>1.35873540139658</v>
       </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I189">
+        <v>194.809353722514</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>4</v>
       </c>
@@ -7884,8 +8454,11 @@
       <c r="H190">
         <v>3.5669045109589002</v>
       </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I190">
+        <v>203.64513706346199</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>4</v>
       </c>
@@ -7910,8 +8483,11 @@
       <c r="H191">
         <v>3.6297042068557901</v>
       </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I191">
+        <v>144.581598667777</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>4</v>
       </c>
@@ -7936,8 +8512,11 @@
       <c r="H192">
         <v>1.64735686519184</v>
       </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I192">
+        <v>218.86779013203599</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>4</v>
       </c>
@@ -7962,8 +8541,11 @@
       <c r="H193">
         <v>1.5658526338066101</v>
       </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I193">
+        <v>164.64055023923399</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>4</v>
       </c>
@@ -7988,8 +8570,11 @@
       <c r="H194">
         <v>1.60255102511932</v>
       </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I194">
+        <v>195.70003581661899</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>4</v>
       </c>
@@ -8014,8 +8599,11 @@
       <c r="H195">
         <v>1.1089419504273501</v>
       </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I195">
+        <v>45.778156996587001</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>4</v>
       </c>
@@ -8040,8 +8628,11 @@
       <c r="H196">
         <v>0.92822882923856598</v>
       </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I196">
+        <v>58.732549019607802</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>4</v>
       </c>
@@ -8066,8 +8657,11 @@
       <c r="H197">
         <v>1.106860771529</v>
       </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I197">
+        <v>49.911016949152497</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>4</v>
       </c>
@@ -8092,8 +8686,11 @@
       <c r="H198">
         <v>1.2367541686638699</v>
       </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I198">
+        <v>20.7209302325581</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>4</v>
       </c>
@@ -8118,8 +8715,11 @@
       <c r="H199">
         <v>1.2548455959790199</v>
       </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I199">
+        <v>57.807792207792197</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>4</v>
       </c>
@@ -8144,8 +8744,11 @@
       <c r="H200">
         <v>1.1325088750979899</v>
       </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I200">
+        <v>40.474103585657403</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>4</v>
       </c>
@@ -8170,8 +8773,11 @@
       <c r="H201">
         <v>2.3732202704954002</v>
       </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I201">
+        <v>63.631147540983598</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>4</v>
       </c>
@@ -8196,8 +8802,11 @@
       <c r="H202">
         <v>2.37208603832753</v>
       </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I202">
+        <v>70.254409769335098</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>4</v>
       </c>
@@ -8222,8 +8831,11 @@
       <c r="H203">
         <v>1.17212438144753</v>
       </c>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I203">
+        <v>70.998750000000001</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>4</v>
       </c>
@@ -8248,8 +8860,11 @@
       <c r="H204">
         <v>1.3491844351697699</v>
       </c>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I204">
+        <v>58.234906695938498</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>4</v>
       </c>
@@ -8274,8 +8889,11 @@
       <c r="H205">
         <v>2.2464038477193</v>
       </c>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I205">
+        <v>72.081982840800805</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>4</v>
       </c>
@@ -8300,8 +8918,11 @@
       <c r="H206">
         <v>1.21989262237933</v>
       </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I206">
+        <v>52.5699658703072</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>4</v>
       </c>
@@ -8326,8 +8947,11 @@
       <c r="H207">
         <v>1.0708013877506499</v>
       </c>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I207">
+        <v>43.75</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>4</v>
       </c>
@@ -8352,8 +8976,11 @@
       <c r="H208">
         <v>1.2255795643030001</v>
       </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I208">
+        <v>66.182092555332005</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>4</v>
       </c>
@@ -8378,8 +9005,11 @@
       <c r="H209">
         <v>1.08918386592237</v>
       </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I209">
+        <v>43.475982532751097</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>4</v>
       </c>
@@ -8404,8 +9034,11 @@
       <c r="H210">
         <v>0.93320000916405899</v>
       </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I210">
+        <v>73.470144927536197</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>4</v>
       </c>
@@ -8430,8 +9063,11 @@
       <c r="H211">
         <v>1.46093344442408</v>
       </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I211">
+        <v>63.504580690627201</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>4</v>
       </c>
@@ -8456,8 +9092,11 @@
       <c r="H212">
         <v>1.98734506268776</v>
       </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I212">
+        <v>63.412133891213401</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>4</v>
       </c>
@@ -8482,8 +9121,11 @@
       <c r="H213">
         <v>1.01915984522767</v>
       </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I213">
+        <v>55.536115569823401</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>4</v>
       </c>
@@ -8508,8 +9150,11 @@
       <c r="H214">
         <v>0.93059260683044898</v>
       </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I214">
+        <v>48.665678280207601</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>4</v>
       </c>
@@ -8534,8 +9179,11 @@
       <c r="H215">
         <v>1.0665325067943201</v>
       </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I215">
+        <v>44.448979591836697</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>4</v>
       </c>
@@ -8560,8 +9208,11 @@
       <c r="H216">
         <v>1.54888552545503</v>
       </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I216">
+        <v>153.97431253087399</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>4</v>
       </c>
@@ -8586,8 +9237,11 @@
       <c r="H217">
         <v>1.0913918636893201</v>
       </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I217">
+        <v>106.868334700574</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>4</v>
       </c>
@@ -8612,8 +9266,11 @@
       <c r="H218">
         <v>2.3409484680292501</v>
       </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I218">
+        <v>96.9888147566719</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>4</v>
       </c>
@@ -8638,8 +9295,11 @@
       <c r="H219">
         <v>0.61989636249585101</v>
       </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I219">
+        <v>45.7777777777778</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>4</v>
       </c>
@@ -8664,8 +9324,11 @@
       <c r="H220">
         <v>1.1229265216867499</v>
       </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I220">
+        <v>69.052957746478896</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>4</v>
       </c>
@@ -8690,8 +9353,11 @@
       <c r="H221">
         <v>0.49843000122388997</v>
       </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I221">
+        <v>82.884778012685004</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>4</v>
       </c>
@@ -8716,8 +9382,11 @@
       <c r="H222">
         <v>1.34313561503362</v>
       </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I222">
+        <v>46.793261868300199</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>4</v>
       </c>
@@ -8742,8 +9411,11 @@
       <c r="H223">
         <v>0.42991368198951901</v>
       </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I223">
+        <v>65.726541554959795</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>4</v>
       </c>
@@ -8768,8 +9440,11 @@
       <c r="H224">
         <v>0.62485114161640498</v>
       </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I224">
+        <v>55.289972899729001</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>4</v>
       </c>
@@ -8794,8 +9469,11 @@
       <c r="H225">
         <v>0.61167755941715796</v>
       </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I225">
+        <v>52.392971246006397</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>4</v>
       </c>
@@ -8820,8 +9498,11 @@
       <c r="H226">
         <v>0.485863159949112</v>
       </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I226">
+        <v>53.917857142857102</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>4</v>
       </c>
@@ -8846,8 +9527,11 @@
       <c r="H227">
         <v>0.35809197602091702</v>
       </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I227">
+        <v>64.47</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>4</v>
       </c>
@@ -8872,8 +9556,11 @@
       <c r="H228">
         <v>0.85738900018447595</v>
       </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I228">
+        <v>41.312406576980599</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>4</v>
       </c>
@@ -8898,8 +9585,11 @@
       <c r="H229">
         <v>0.67265330981868199</v>
       </c>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I229">
+        <v>69.647457627118598</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>4</v>
       </c>
@@ -8924,8 +9614,11 @@
       <c r="H230">
         <v>1.35872875207943</v>
       </c>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I230">
+        <v>46.4677419354839</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>4</v>
       </c>
@@ -8950,8 +9643,11 @@
       <c r="H231">
         <v>0.47999774769834103</v>
       </c>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I231">
+        <v>79.149425287356294</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>4</v>
       </c>
@@ -8976,8 +9672,11 @@
       <c r="H232">
         <v>0.40860832646432699</v>
       </c>
-    </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I232">
+        <v>47.375757575757603</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>4</v>
       </c>
@@ -9002,8 +9701,11 @@
       <c r="H233">
         <v>0.58021189255989003</v>
       </c>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I233">
+        <v>32.495384615384602</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>4</v>
       </c>
@@ -9028,8 +9730,11 @@
       <c r="H234">
         <v>0.61191662604384101</v>
       </c>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I234">
+        <v>74.525606469002696</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>4</v>
       </c>
@@ -9054,8 +9759,11 @@
       <c r="H235">
         <v>0.61426985332049999</v>
       </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I235">
+        <v>143.45521023766</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>4</v>
       </c>
@@ -9080,8 +9788,11 @@
       <c r="H236">
         <v>0.35744553102020599</v>
       </c>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I236">
+        <v>83.051762940735202</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>4</v>
       </c>
@@ -9106,8 +9817,11 @@
       <c r="H237">
         <v>0.583745668259813</v>
       </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I237">
+        <v>94.025943396226396</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>4</v>
       </c>
@@ -9132,8 +9846,11 @@
       <c r="H238">
         <v>0.41817747024323798</v>
       </c>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I238">
+        <v>47.527559055118097</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>4</v>
       </c>
@@ -9158,8 +9875,11 @@
       <c r="H239">
         <v>0.81850410291364695</v>
       </c>
-    </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I239">
+        <v>63.706336939721801</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>4</v>
       </c>
@@ -9184,8 +9904,11 @@
       <c r="H240">
         <v>2.7092574626364399</v>
       </c>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I240">
+        <v>60.183999999999997</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>4</v>
       </c>
@@ -9210,8 +9933,11 @@
       <c r="H241">
         <v>0.91273350825430299</v>
       </c>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I241">
+        <v>100.8</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>4</v>
       </c>
@@ -9236,8 +9962,11 @@
       <c r="H242">
         <v>1.54913649454629</v>
       </c>
-    </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I242">
+        <v>120.062355658199</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>4</v>
       </c>
@@ -9262,8 +9991,11 @@
       <c r="H243">
         <v>1.03279014010327</v>
       </c>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I243">
+        <v>67.369885433715197</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>4</v>
       </c>
@@ -9288,8 +10020,11 @@
       <c r="H244">
         <v>0.716837020310506</v>
       </c>
-    </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I244">
+        <v>118.76359338061501</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>4</v>
       </c>
@@ -9314,8 +10049,11 @@
       <c r="H245">
         <v>1.1470914621569299</v>
       </c>
-    </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I245">
+        <v>115.50846660395101</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>4</v>
       </c>
@@ -9340,8 +10078,11 @@
       <c r="H246">
         <v>2.7179553102143799</v>
       </c>
-    </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I246">
+        <v>36.515151515151501</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>4</v>
       </c>
@@ -9366,8 +10107,11 @@
       <c r="H247">
         <v>2.9285949638759798</v>
       </c>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I247">
+        <v>51.845454545454501</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>4</v>
       </c>
@@ -9392,8 +10136,11 @@
       <c r="H248">
         <v>0.57434076727412597</v>
       </c>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I248">
+        <v>85.367041198501894</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>4</v>
       </c>
@@ -9418,8 +10165,11 @@
       <c r="H249">
         <v>1.1912251404222001</v>
       </c>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I249">
+        <v>99.483156437471195</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>4</v>
       </c>
@@ -9444,8 +10194,11 @@
       <c r="H250">
         <v>1.07019102933985</v>
       </c>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I250">
+        <v>103.018042646255</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>4</v>
       </c>
@@ -9470,8 +10223,11 @@
       <c r="H251">
         <v>1.21192501244813</v>
       </c>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I251">
+        <v>102.035169988277</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>4</v>
       </c>
@@ -9496,8 +10252,11 @@
       <c r="H252">
         <v>1.0083026484878099</v>
       </c>
-    </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I252">
+        <v>129.547557840617</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>4</v>
       </c>
@@ -9522,8 +10281,11 @@
       <c r="H253">
         <v>1.47941388984387</v>
       </c>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I253">
+        <v>137.111074918567</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>4</v>
       </c>
@@ -9548,8 +10310,11 @@
       <c r="H254">
         <v>1.91232708590786</v>
       </c>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I254">
+        <v>80.890455531453398</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>4</v>
       </c>
@@ -9574,8 +10339,11 @@
       <c r="H255">
         <v>1.8945366232492999</v>
       </c>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I255">
+        <v>101.325627476882</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>4</v>
       </c>
@@ -9600,8 +10368,11 @@
       <c r="H256">
         <v>3.4264097664106101</v>
       </c>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I256">
+        <v>56.514631685166499</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>4</v>
       </c>
@@ -9626,8 +10397,11 @@
       <c r="H257">
         <v>1.76636909597586</v>
       </c>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I257">
+        <v>59.167305236270799</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>4</v>
       </c>
@@ -9652,8 +10426,11 @@
       <c r="H258">
         <v>1.7747111801695701</v>
       </c>
-    </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I258">
+        <v>98.845105328376704</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>4</v>
       </c>
@@ -9678,8 +10455,11 @@
       <c r="H259">
         <v>2.0616199121632399</v>
       </c>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I259">
+        <v>76.3632218844985</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>4</v>
       </c>
@@ -9704,8 +10484,11 @@
       <c r="H260">
         <v>2.3357582184837198</v>
       </c>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I260">
+        <v>78.4721283783784</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>4</v>
       </c>
@@ -9730,8 +10513,11 @@
       <c r="H261">
         <v>1.5381558609215</v>
       </c>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I261">
+        <v>89.104255319148905</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>269</v>
       </c>
@@ -9756,8 +10542,11 @@
       <c r="H262">
         <v>2.22938957734904</v>
       </c>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I262">
+        <v>38.745810055865903</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>269</v>
       </c>
@@ -9782,8 +10571,11 @@
       <c r="H263">
         <v>1.3604673739795601</v>
       </c>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I263">
+        <v>88.275512087100907</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>269</v>
       </c>
@@ -9808,8 +10600,11 @@
       <c r="H264">
         <v>1.8621303571754799</v>
       </c>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I264">
+        <v>107.119867929945</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>269</v>
       </c>
@@ -9834,8 +10629,11 @@
       <c r="H265">
         <v>1.3591130853040401</v>
       </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I265">
+        <v>104.936493638104</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>269</v>
       </c>
@@ -9860,8 +10658,11 @@
       <c r="H266">
         <v>1.42838550298239</v>
       </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I266">
+        <v>103.434114986311</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>269</v>
       </c>
@@ -9886,8 +10687,11 @@
       <c r="H267">
         <v>1.5249947483195101</v>
       </c>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I267">
+        <v>88.983987370320193</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>269</v>
       </c>
@@ -9912,8 +10716,11 @@
       <c r="H268">
         <v>2.2859382404200299</v>
       </c>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I268">
+        <v>86.292526491912994</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>269</v>
       </c>
@@ -9938,8 +10745,11 @@
       <c r="H269">
         <v>2.45525366400501</v>
       </c>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I269">
+        <v>147.54366259222601</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>269</v>
       </c>
@@ -9964,8 +10774,11 @@
       <c r="H270">
         <v>1.41555447639565</v>
       </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I270">
+        <v>67.096945923227807</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>269</v>
       </c>
@@ -9990,8 +10803,11 @@
       <c r="H271">
         <v>2.1259838097352701</v>
       </c>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I271">
+        <v>90.740633245382597</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>269</v>
       </c>
@@ -10016,8 +10832,11 @@
       <c r="H272">
         <v>1.8483254668996201</v>
       </c>
-    </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I272">
+        <v>131.455694203127</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>269</v>
       </c>
@@ -10042,8 +10861,11 @@
       <c r="H273">
         <v>2.0742500932795398</v>
       </c>
-    </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I273">
+        <v>68.654084340902401</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>269</v>
       </c>
@@ -10068,8 +10890,11 @@
       <c r="H274">
         <v>2.50135824611844</v>
       </c>
-    </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I274">
+        <v>71.2216193656093</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>269</v>
       </c>
@@ -10094,8 +10919,11 @@
       <c r="H275">
         <v>4.8967848361950299</v>
       </c>
-    </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I275">
+        <v>87.252087682672197</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>269</v>
       </c>
@@ -10120,8 +10948,11 @@
       <c r="H276">
         <v>2.17952117787679</v>
       </c>
-    </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I276">
+        <v>83.735971542908004</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>269</v>
       </c>
@@ -10146,8 +10977,11 @@
       <c r="H277">
         <v>1.4352633334392499</v>
       </c>
-    </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I277">
+        <v>48.129524554881598</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>269</v>
       </c>
@@ -10172,8 +11006,11 @@
       <c r="H278">
         <v>1.5150343008431399</v>
       </c>
-    </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I278">
+        <v>84.426773455377599</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>269</v>
       </c>
@@ -10198,8 +11035,11 @@
       <c r="H279">
         <v>1.80321931968903</v>
       </c>
-    </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I279">
+        <v>110.636535507503</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>269</v>
       </c>
@@ -10224,8 +11064,11 @@
       <c r="H280">
         <v>3.1548146487693001</v>
       </c>
-    </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I280">
+        <v>119.509536784741</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>269</v>
       </c>
@@ -10250,8 +11093,11 @@
       <c r="H281">
         <v>1.3329795273163501</v>
       </c>
-    </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I281">
+        <v>74.861129867206799</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>269</v>
       </c>
@@ -10276,8 +11122,11 @@
       <c r="H282">
         <v>2.3736469573584502</v>
       </c>
-    </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I282">
+        <v>121.037165082109</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>269</v>
       </c>
@@ -10302,8 +11151,11 @@
       <c r="H283">
         <v>2.7696171152261302</v>
       </c>
-    </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I283">
+        <v>104.095740194011</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>269</v>
       </c>
@@ -10328,8 +11180,11 @@
       <c r="H284">
         <v>4.0116952038453597</v>
       </c>
-    </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I284">
+        <v>115.476760943974</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>269</v>
       </c>
@@ -10354,8 +11209,11 @@
       <c r="H285">
         <v>2.5118455348592099</v>
       </c>
-    </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I285">
+        <v>173.36501408879701</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>269</v>
       </c>
@@ -10380,8 +11238,11 @@
       <c r="H286">
         <v>3.2425323077776498</v>
       </c>
-    </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I286">
+        <v>169.84436435124499</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>269</v>
       </c>
@@ -10406,8 +11267,11 @@
       <c r="H287">
         <v>3.8710754975803798</v>
       </c>
-    </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I287">
+        <v>256.220916286879</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>269</v>
       </c>
@@ -10432,8 +11296,11 @@
       <c r="H288">
         <v>3.4755638131791597</v>
       </c>
-    </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I288">
+        <v>205.04902833973398</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>269</v>
       </c>
@@ -10458,8 +11325,11 @@
       <c r="H289">
         <v>1.7548118524156</v>
       </c>
-    </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I289">
+        <v>91.253717061681101</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>269</v>
       </c>
@@ -10484,8 +11354,11 @@
       <c r="H290">
         <v>1.70447032578362</v>
       </c>
-    </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I290">
+        <v>96.219173982442101</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>269</v>
       </c>
@@ -10510,8 +11383,11 @@
       <c r="H291">
         <v>1.8135274271893</v>
       </c>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I291">
+        <v>97.864550264550303</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>269</v>
       </c>
@@ -10536,8 +11412,11 @@
       <c r="H292">
         <v>2.2035156036522499</v>
       </c>
-    </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I292">
+        <v>88.2255572721254</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>269</v>
       </c>
@@ -10562,8 +11441,11 @@
       <c r="H293">
         <v>1.75537346944671</v>
       </c>
-    </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I293">
+        <v>56.213730841906397</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>269</v>
       </c>
@@ -10588,8 +11470,11 @@
       <c r="H294">
         <v>2.2441120570263999</v>
       </c>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I294">
+        <v>64.792823789628898</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>269</v>
       </c>
@@ -10614,8 +11499,11 @@
       <c r="H295">
         <v>1.90028013354022</v>
       </c>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I295">
+        <v>56.337379656760099</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>269</v>
       </c>
@@ -10640,8 +11528,11 @@
       <c r="H296">
         <v>2.1259841610492201</v>
       </c>
-    </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I296">
+        <v>71.067313288069798</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>269</v>
       </c>
@@ -10666,8 +11557,11 @@
       <c r="H297">
         <v>1.52991756396755</v>
       </c>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I297">
+        <v>51.5078125</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>269</v>
       </c>
@@ -10692,8 +11586,11 @@
       <c r="H298">
         <v>1.3218110191993699</v>
       </c>
-    </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I298">
+        <v>54.064716863721202</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>269</v>
       </c>
@@ -10718,8 +11615,11 @@
       <c r="H299">
         <v>2.3503938925000001</v>
       </c>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I299">
+        <v>179.45648282328901</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>269</v>
       </c>
@@ -10744,8 +11644,11 @@
       <c r="H300">
         <v>2.48999517510804</v>
       </c>
-    </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I300">
+        <v>125.957035964277</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>269</v>
       </c>
@@ -10770,8 +11673,11 @@
       <c r="H301">
         <v>1.8530504673528101</v>
       </c>
-    </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I301">
+        <v>126.8239318162455</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>269</v>
       </c>
@@ -10796,8 +11702,11 @@
       <c r="H302">
         <v>2.345854470223705</v>
       </c>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I302">
+        <v>136.821145723337</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>269</v>
       </c>
@@ -10822,8 +11731,11 @@
       <c r="H303">
         <v>1.6543660910040601</v>
       </c>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I303">
+        <v>95.706548347613193</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>269</v>
       </c>
@@ -10848,8 +11760,11 @@
       <c r="H304">
         <v>1.6301554836096499</v>
       </c>
-    </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I304">
+        <v>71.239673635900004</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>269</v>
       </c>
@@ -10874,8 +11789,11 @@
       <c r="H305">
         <v>1.9995933030619299</v>
       </c>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I305">
+        <v>94.814980602805093</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>269</v>
       </c>
@@ -10900,8 +11818,11 @@
       <c r="H306">
         <v>1.6114855228164</v>
       </c>
-    </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I306">
+        <v>89.229304271246093</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>408</v>
       </c>
@@ -10926,8 +11847,11 @@
       <c r="H307">
         <v>5.9203734459350299</v>
       </c>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I307">
+        <v>51.245927691696501</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>408</v>
       </c>
@@ -10952,8 +11876,11 @@
       <c r="H308">
         <v>1.72647339300497</v>
       </c>
-    </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I308">
+        <v>64.479233226837096</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>408</v>
       </c>
@@ -10978,8 +11905,11 @@
       <c r="H309">
         <v>2.2105908956337399</v>
       </c>
-    </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I309">
+        <v>69.688085676037502</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>408</v>
       </c>
@@ -11004,8 +11934,11 @@
       <c r="H310">
         <v>1.9344294796835699</v>
       </c>
-    </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I310">
+        <v>95.278626753192398</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>408</v>
       </c>
@@ -11030,8 +11963,11 @@
       <c r="H311">
         <v>1.4009783158985001</v>
       </c>
-    </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I311">
+        <v>94.982162764771502</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>408</v>
       </c>
@@ -11056,8 +11992,11 @@
       <c r="H312">
         <v>1.8495620927258201</v>
       </c>
-    </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I312">
+        <v>64.721100917431201</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>408</v>
       </c>
@@ -11082,8 +12021,11 @@
       <c r="H313">
         <v>1.54207307722992</v>
       </c>
-    </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I313">
+        <v>102.58381294964001</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>408</v>
       </c>
@@ -11108,8 +12050,11 @@
       <c r="H314">
         <v>3.2102015528720602</v>
       </c>
-    </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I314">
+        <v>243.35881696428601</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>408</v>
       </c>
@@ -11134,8 +12079,11 @@
       <c r="H315">
         <v>1.5762463049904001</v>
       </c>
-    </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I315">
+        <v>96.120044876589404</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>408</v>
       </c>
@@ -11160,8 +12108,11 @@
       <c r="H316">
         <v>1.7565153568890599</v>
       </c>
-    </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I316">
+        <v>128.225401606426</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>408</v>
       </c>
@@ -11186,8 +12137,11 @@
       <c r="H317">
         <v>1.89252639043288</v>
       </c>
-    </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I317">
+        <v>114.483113354037</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>408</v>
       </c>
@@ -11212,8 +12166,11 @@
       <c r="H318">
         <v>1.6574641166631501</v>
       </c>
-    </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I318">
+        <v>131.24094674556201</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>408</v>
       </c>
@@ -11238,8 +12195,11 @@
       <c r="H319">
         <v>1.84836776054302</v>
       </c>
-    </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I319">
+        <v>87.023026315789494</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>408</v>
       </c>
@@ -11264,8 +12224,11 @@
       <c r="H320">
         <v>2.3309075425628301</v>
       </c>
-    </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I320">
+        <v>68.730538922155702</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>408</v>
       </c>
@@ -11290,8 +12253,11 @@
       <c r="H321">
         <v>1.5565857505882399</v>
       </c>
-    </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I321">
+        <v>63.219512195122</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>408</v>
       </c>
@@ -11316,8 +12282,11 @@
       <c r="H322">
         <v>1.5457825067195801</v>
       </c>
-    </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I322">
+        <v>67.000355998575998</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>408</v>
       </c>
@@ -11342,8 +12311,11 @@
       <c r="H323">
         <v>1.5682296746037601</v>
       </c>
-    </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I323">
+        <v>84.054221251819499</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>408</v>
       </c>
@@ -11368,8 +12340,11 @@
       <c r="H324">
         <v>1.9418642456900701</v>
       </c>
-    </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I324">
+        <v>164.54296767062701</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>408</v>
       </c>
@@ -11394,8 +12369,11 @@
       <c r="H325">
         <v>3.2700694356642002</v>
       </c>
-    </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I325">
+        <v>129.896161107615</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>408</v>
       </c>
@@ -11420,8 +12398,11 @@
       <c r="H326">
         <v>2.2685030807663602</v>
       </c>
-    </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I326">
+        <v>147.282308494007</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>408</v>
       </c>
@@ -11446,8 +12427,11 @@
       <c r="H327">
         <v>1.52487709317218</v>
       </c>
-    </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I327">
+        <v>255.839657498094</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>408</v>
       </c>
@@ -11472,8 +12456,11 @@
       <c r="H328">
         <v>1.3953225804878</v>
       </c>
-    </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I328">
+        <v>83.552985702270803</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>408</v>
       </c>
@@ -11498,8 +12485,11 @@
       <c r="H329">
         <v>1.80380863148519</v>
       </c>
-    </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I329">
+        <v>126.72043334336399</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>408</v>
       </c>
@@ -11524,8 +12514,11 @@
       <c r="H330">
         <v>1.14082329021739</v>
       </c>
-    </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I330">
+        <v>151.61872415829899</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>408</v>
       </c>
@@ -11550,8 +12543,11 @@
       <c r="H331">
         <v>2.7240402238243702</v>
       </c>
-    </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I331">
+        <v>191.213063320023</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>408</v>
       </c>
@@ -11576,8 +12572,11 @@
       <c r="H332">
         <v>2.4930078027973099</v>
       </c>
-    </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I332">
+        <v>197.98910788381701</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>408</v>
       </c>
@@ -11602,8 +12601,11 @@
       <c r="H333">
         <v>4.6285614684271001</v>
       </c>
-    </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I333">
+        <v>432.97860314897099</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>408</v>
       </c>
@@ -11628,8 +12630,11 @@
       <c r="H334">
         <v>3.0491263900332202</v>
       </c>
-    </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I334">
+        <v>97.453974895397494</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>408</v>
       </c>
@@ -11654,8 +12659,11 @@
       <c r="H335">
         <v>1.9159293118848</v>
       </c>
-    </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I335">
+        <v>126.227664287472</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>408</v>
       </c>
@@ -11680,8 +12688,11 @@
       <c r="H336">
         <v>2.1813425300859599</v>
       </c>
-    </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I336">
+        <v>123.72011661807601</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>408</v>
       </c>
@@ -11706,8 +12717,11 @@
       <c r="H337">
         <v>1.88356527071465</v>
       </c>
-    </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I337">
+        <v>81.431886982845597</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>408</v>
       </c>
@@ -11732,8 +12746,11 @@
       <c r="H338">
         <v>1.3287858872947</v>
       </c>
-    </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I338">
+        <v>70.317470664928294</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>408</v>
       </c>
@@ -11758,8 +12775,11 @@
       <c r="H339">
         <v>2.0908538536139201</v>
       </c>
-    </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I339">
+        <v>97.528853359980005</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>408</v>
       </c>
@@ -11784,8 +12804,11 @@
       <c r="H340">
         <v>1.5112285902439</v>
       </c>
-    </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I340">
+        <v>68.109151572926606</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>408</v>
       </c>
@@ -11810,8 +12833,11 @@
       <c r="H341">
         <v>1.52149432878672</v>
       </c>
-    </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I341">
+        <v>123.325538743696</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>408</v>
       </c>
@@ -11836,8 +12862,11 @@
       <c r="H342">
         <v>2.4054002819914699</v>
       </c>
-    </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I342">
+        <v>135.953937007874</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>408</v>
       </c>
@@ -11862,8 +12891,11 @@
       <c r="H343">
         <v>2.15753147494982</v>
       </c>
-    </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I343">
+        <v>64.961671207992694</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>408</v>
       </c>
@@ -11888,8 +12920,11 @@
       <c r="H344">
         <v>2.5586178120115202</v>
       </c>
-    </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I344">
+        <v>78.748755266181504</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>408</v>
       </c>
@@ -11914,8 +12949,11 @@
       <c r="H345">
         <v>2.0738236955417202</v>
       </c>
-    </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I345">
+        <v>100.835489382475</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>408</v>
       </c>
@@ -11940,8 +12978,11 @@
       <c r="H346">
         <v>1.35846886109887</v>
       </c>
-    </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I346">
+        <v>91.1621939736347</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>408</v>
       </c>
@@ -11966,8 +13007,11 @@
       <c r="H347">
         <v>3.0159286099123399</v>
       </c>
-    </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I347">
+        <v>102.100945410186</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>408</v>
       </c>
@@ -11992,8 +13036,11 @@
       <c r="H348">
         <v>1.6900201765709</v>
       </c>
-    </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I348">
+        <v>64.124936772888205</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>408</v>
       </c>
@@ -12018,8 +13065,11 @@
       <c r="H349">
         <v>2.3469277415656702</v>
       </c>
-    </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I349">
+        <v>60.278110944527697</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>408</v>
       </c>
@@ -12044,8 +13094,11 @@
       <c r="H350">
         <v>1.3222616921950701</v>
       </c>
-    </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I350">
+        <v>92.445353594389204</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>408</v>
       </c>
@@ -12070,8 +13123,11 @@
       <c r="H351">
         <v>2.6482345121363702</v>
       </c>
-    </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I351">
+        <v>120.291237113402</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>408</v>
       </c>
@@ -12096,8 +13152,11 @@
       <c r="H352">
         <v>1.3110620371137101</v>
       </c>
-    </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I352">
+        <v>75.476623376623394</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>408</v>
       </c>
@@ -12122,8 +13181,11 @@
       <c r="H353">
         <v>4.7663021018512</v>
       </c>
-    </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I353">
+        <v>90.543745203376801</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>408</v>
       </c>
@@ -12148,8 +13210,11 @@
       <c r="H354">
         <v>3.52236129098238</v>
       </c>
-    </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I354">
+        <v>106.540825285338</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>408</v>
       </c>
@@ -12174,8 +13239,11 @@
       <c r="H355">
         <v>1.9846520286818199</v>
       </c>
-    </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I355">
+        <v>78.107717041800598</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>408</v>
       </c>
@@ -12200,8 +13268,11 @@
       <c r="H356">
         <v>2.2756398366890398</v>
       </c>
-    </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I356">
+        <v>97.722871452420705</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>408</v>
       </c>
@@ -12226,8 +13297,11 @@
       <c r="H357">
         <v>1.9292693393792</v>
       </c>
-    </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I357">
+        <v>172.666551991055</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>408</v>
       </c>
@@ -12252,8 +13326,11 @@
       <c r="H358">
         <v>1.2061920626689</v>
       </c>
-    </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I358">
+        <v>136.31512605041999</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>408</v>
       </c>
@@ -12278,8 +13355,11 @@
       <c r="H359">
         <v>1.7008462172860599</v>
       </c>
-    </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I359">
+        <v>168.41931789259399</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>408</v>
       </c>
@@ -12304,8 +13384,11 @@
       <c r="H360">
         <v>2.4906103138596598</v>
       </c>
-    </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I360">
+        <v>81.739902352418994</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>408</v>
       </c>
@@ -12330,8 +13413,11 @@
       <c r="H361">
         <v>2.3515794297361099</v>
       </c>
-    </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I361">
+        <v>90.853467287429595</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>408</v>
       </c>
@@ -12356,8 +13442,11 @@
       <c r="H362">
         <v>1.62534359441341</v>
       </c>
-    </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I362">
+        <v>141.02924996645601</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>408</v>
       </c>
@@ -12382,8 +13471,11 @@
       <c r="H363">
         <v>2.0422348792217702</v>
       </c>
-    </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I363">
+        <v>139.12412681354101</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>408</v>
       </c>
@@ -12408,8 +13500,11 @@
       <c r="H364">
         <v>2.0520760696495501</v>
       </c>
-    </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I364">
+        <v>100.58547008547001</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>408</v>
       </c>
@@ -12434,8 +13529,11 @@
       <c r="H365">
         <v>2.1802289410323201</v>
       </c>
-    </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I365">
+        <v>87.719391131700903</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>408</v>
       </c>
@@ -12460,8 +13558,11 @@
       <c r="H366">
         <v>2.5224403177134</v>
       </c>
-    </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I366">
+        <v>88.916163648557998</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>408</v>
       </c>
@@ -12486,8 +13587,11 @@
       <c r="H367">
         <v>2.44888174799283</v>
       </c>
-    </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I367">
+        <v>108.027724867725</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>408</v>
       </c>
@@ -12512,8 +13616,11 @@
       <c r="H368">
         <v>2.0939791243644401</v>
       </c>
-    </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I368">
+        <v>69.475106685632994</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>408</v>
       </c>
@@ -12538,8 +13645,11 @@
       <c r="H369">
         <v>3.6764992492548401</v>
       </c>
-    </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I369">
+        <v>158.51452599388401</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>408</v>
       </c>
@@ -12564,8 +13674,11 @@
       <c r="H370">
         <v>3.1548186544766699</v>
       </c>
-    </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I370">
+        <v>166.53863037752399</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>408</v>
       </c>
@@ -12590,8 +13703,11 @@
       <c r="H371">
         <v>3.3022225379474901</v>
       </c>
-    </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I371">
+        <v>147.84605158202601</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>408</v>
       </c>
@@ -12616,8 +13732,11 @@
       <c r="H372">
         <v>1.2263496303252801</v>
       </c>
-    </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I372">
+        <v>156.27873165328199</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>408</v>
       </c>
@@ -12642,8 +13761,11 @@
       <c r="H373">
         <v>5.3769097338501304</v>
       </c>
-    </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I373">
+        <v>126.20651068158701</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>408</v>
       </c>
@@ -12668,8 +13790,11 @@
       <c r="H374">
         <v>3.3702505173333299</v>
       </c>
-    </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I374">
+        <v>291.38470496894399</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>408</v>
       </c>
@@ -12694,8 +13819,11 @@
       <c r="H375">
         <v>1.4802884306861801</v>
       </c>
-    </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I375">
+        <v>85.867856281649395</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>408</v>
       </c>
@@ -12720,8 +13848,11 @@
       <c r="H376">
         <v>1.48634277528721</v>
       </c>
-    </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I376">
+        <v>158.64136752136801</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>408</v>
       </c>
@@ -12746,8 +13877,11 @@
       <c r="H377">
         <v>1.4023904855098499</v>
       </c>
-    </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I377">
+        <v>85.7225628448804</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>408</v>
       </c>
@@ -12772,8 +13906,11 @@
       <c r="H378">
         <v>2.70625507790571</v>
       </c>
-    </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I378">
+        <v>94.385493761894693</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>408</v>
       </c>
@@ -12798,8 +13935,11 @@
       <c r="H379">
         <v>2.7931730353958599</v>
       </c>
-    </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I379">
+        <v>81.812468827930203</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>408</v>
       </c>
@@ -12824,8 +13964,11 @@
       <c r="H380">
         <v>2.1034446457060301</v>
       </c>
-    </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I380">
+        <v>89.409013120365103</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>408</v>
       </c>
@@ -12850,8 +13993,11 @@
       <c r="H381">
         <v>1.5891542482087799</v>
       </c>
-    </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I381">
+        <v>93.472026523000395</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>408</v>
       </c>
@@ -12876,8 +14022,11 @@
       <c r="H382">
         <v>1.12274337896702</v>
       </c>
-    </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I382">
+        <v>131.45436207765999</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>408</v>
       </c>
@@ -12902,8 +14051,11 @@
       <c r="H383">
         <v>1.9430058090150499</v>
       </c>
-    </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I383">
+        <v>125.931095931096</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>408</v>
       </c>
@@ -12928,8 +14080,11 @@
       <c r="H384">
         <v>2.1598034947725302</v>
       </c>
-    </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I384">
+        <v>163.96827262044701</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>408</v>
       </c>
@@ -12954,8 +14109,11 @@
       <c r="H385">
         <v>1.6705166606606601</v>
       </c>
-    </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I385">
+        <v>132.025344352617</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>408</v>
       </c>
@@ -12980,8 +14138,11 @@
       <c r="H386">
         <v>2.2894082189823601</v>
       </c>
-    </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I386">
+        <v>86.068313189700504</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>408</v>
       </c>
@@ -13006,8 +14167,11 @@
       <c r="H387">
         <v>1.5829804961883001</v>
       </c>
-    </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I387">
+        <v>151.9</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>408</v>
       </c>
@@ -13032,8 +14196,11 @@
       <c r="H388">
         <v>4.5361547335984103</v>
       </c>
-    </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I388">
+        <v>147.583959899749</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>408</v>
       </c>
@@ -13058,8 +14225,11 @@
       <c r="H389">
         <v>2.2910393992707401</v>
       </c>
-    </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I389">
+        <v>118.86280193236701</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>408</v>
       </c>
@@ -13084,8 +14254,11 @@
       <c r="H390">
         <v>2.7279322347651598</v>
       </c>
-    </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I390">
+        <v>151.16114542391901</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>408</v>
       </c>
@@ -13110,8 +14283,11 @@
       <c r="H391">
         <v>2.5806732642640502</v>
       </c>
-    </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I391">
+        <v>149.362331225432</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>408</v>
       </c>
@@ -13136,8 +14312,11 @@
       <c r="H392">
         <v>2.0368175265255299</v>
       </c>
-    </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I392">
+        <v>81.2078745412079</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>408</v>
       </c>
@@ -13162,8 +14341,11 @@
       <c r="H393">
         <v>1.5660099010322399</v>
       </c>
-    </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I393">
+        <v>88.588394793926199</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>408</v>
       </c>
@@ -13188,8 +14370,11 @@
       <c r="H394">
         <v>1.6469439859392601</v>
       </c>
-    </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I394">
+        <v>90.103864734299506</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>408</v>
       </c>
@@ -13214,8 +14399,11 @@
       <c r="H395">
         <v>1.91820572083812</v>
       </c>
-    </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I395">
+        <v>114.856262833676</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>408</v>
       </c>
@@ -13240,8 +14428,11 @@
       <c r="H396">
         <v>1.4293565555987</v>
       </c>
-    </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I396">
+        <v>92.657968883988701</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>408</v>
       </c>
@@ -13266,8 +14457,11 @@
       <c r="H397">
         <v>2.07378855922006</v>
       </c>
-    </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I397">
+        <v>99.966048412448899</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>408</v>
       </c>
@@ -13292,8 +14486,11 @@
       <c r="H398">
         <v>1.20469952879522</v>
       </c>
-    </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I398">
+        <v>63.8968903436989</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>408</v>
       </c>
@@ -13318,8 +14515,11 @@
       <c r="H399">
         <v>3.6727411037401101</v>
       </c>
-    </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I399">
+        <v>156.32754491017999</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>408</v>
       </c>
@@ -13344,8 +14544,11 @@
       <c r="H400">
         <v>5.0168235985244403</v>
       </c>
-    </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I400">
+        <v>227.50403026813601</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>408</v>
       </c>
@@ -13370,8 +14573,11 @@
       <c r="H401">
         <v>1.7406982386963801</v>
       </c>
-    </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I401">
+        <v>106.871123097669</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>408</v>
       </c>
@@ -13396,8 +14602,11 @@
       <c r="H402">
         <v>1.3071014028157999</v>
       </c>
-    </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I402">
+        <v>87.479642502482605</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>408</v>
       </c>
@@ -13422,8 +14631,11 @@
       <c r="H403">
         <v>1.7048237169165401</v>
       </c>
-    </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I403">
+        <v>62.942727272727304</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>408</v>
       </c>
@@ -13448,8 +14660,11 @@
       <c r="H404">
         <v>2.13029417546722</v>
       </c>
-    </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I404">
+        <v>96.285136501516703</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>408</v>
       </c>
@@ -13474,8 +14689,11 @@
       <c r="H405">
         <v>1.65155694017204</v>
       </c>
-    </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I405">
+        <v>168.19270722917099</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>408</v>
       </c>
@@ -13500,8 +14718,11 @@
       <c r="H406">
         <v>2.3258582886308501</v>
       </c>
-    </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I406">
+        <v>242.06443129520099</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>408</v>
       </c>
@@ -13526,8 +14747,11 @@
       <c r="H407">
         <v>1.6813972812170199</v>
       </c>
-    </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I407">
+        <v>120.82120222777</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>408</v>
       </c>
@@ -13552,8 +14776,11 @@
       <c r="H408">
         <v>1.5311704746858199</v>
       </c>
-    </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I408">
+        <v>113.53767421602799</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>408</v>
       </c>
@@ -13578,8 +14805,11 @@
       <c r="H409">
         <v>1.8802744731408301</v>
       </c>
-    </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I409">
+        <v>102.01380408813399</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>408</v>
       </c>
@@ -13604,8 +14834,11 @@
       <c r="H410">
         <v>1.92155478157979</v>
       </c>
-    </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I410">
+        <v>90.305851923698697</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>408</v>
       </c>
@@ -13630,8 +14863,11 @@
       <c r="H411">
         <v>1.2054060055028999</v>
       </c>
-    </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I411">
+        <v>98.265003897116102</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>408</v>
       </c>
@@ -13656,8 +14892,11 @@
       <c r="H412">
         <v>2.5386274762446699</v>
       </c>
-    </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I412">
+        <v>90.368877867327996</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>408</v>
       </c>
@@ -13682,8 +14921,11 @@
       <c r="H413">
         <v>1.9777221111776999</v>
       </c>
-    </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I413">
+        <v>150.43432094536701</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>408</v>
       </c>
@@ -13707,6 +14949,9 @@
       </c>
       <c r="H414">
         <v>2.03185892039519</v>
+      </c>
+      <c r="I414">
+        <v>125.218501628664</v>
       </c>
     </row>
   </sheetData>
